--- a/パターン一覧.xlsx
+++ b/パターン一覧.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="5">
+  <fonts count="7">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -40,10 +40,20 @@
     <font>
       <b val="1"/>
       <color rgb="002D7A3A"/>
-      <sz val="12"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <i val="1"/>
+      <color rgb="00666666"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00CC0000"/>
+      <sz val="11"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
@@ -68,6 +78,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00E9F7EF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFEAEA"/>
       </patternFill>
     </fill>
     <fill>
@@ -102,7 +117,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -116,13 +131,19 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -490,7 +511,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G133"/>
+  <dimension ref="A1:H133"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -499,7 +520,8 @@
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="22" customWidth="1" min="5" max="5"/>
     <col width="62" customWidth="1" min="6" max="6"/>
-    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="50" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="20" customHeight="1">
@@ -538,6 +560,11 @@
           <t>存在</t>
         </is>
       </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>備考</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -575,6 +602,7 @@
           <t>✓</t>
         </is>
       </c>
+      <c r="H2" s="5" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -607,7 +635,12 @@
           <t>RAV4_斜め上_なし_黒</t>
         </is>
       </c>
-      <c r="G3" s="4" t="inlineStr"/>
+      <c r="G3" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="H3" s="5" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -640,7 +673,12 @@
           <t>RAV4_斜め上_なし_カラー1_アーバンカーキー</t>
         </is>
       </c>
-      <c r="G4" s="4" t="inlineStr"/>
+      <c r="G4" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="H4" s="5" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -673,7 +711,12 @@
           <t>RAV4_斜め上_なし_カラー2_レッドマイカ</t>
         </is>
       </c>
-      <c r="G5" s="4" t="inlineStr"/>
+      <c r="G5" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="H5" s="5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -711,6 +754,7 @@
           <t>✓</t>
         </is>
       </c>
+      <c r="H6" s="5" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -748,6 +792,7 @@
           <t>✓</t>
         </is>
       </c>
+      <c r="H7" s="5" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -785,6 +830,7 @@
           <t>✓</t>
         </is>
       </c>
+      <c r="H8" s="5" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -822,6 +868,7 @@
           <t>✓</t>
         </is>
       </c>
+      <c r="H9" s="5" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -859,6 +906,7 @@
           <t>✓</t>
         </is>
       </c>
+      <c r="H10" s="5" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -896,6 +944,7 @@
           <t>✓</t>
         </is>
       </c>
+      <c r="H11" s="5" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -933,6 +982,7 @@
           <t>✓</t>
         </is>
       </c>
+      <c r="H12" s="5" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -970,29 +1020,30 @@
           <t>✓</t>
         </is>
       </c>
+      <c r="H13" s="5" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="5" t="inlineStr">
+      <c r="A14" s="6" t="inlineStr">
         <is>
           <t>RAV4</t>
         </is>
       </c>
-      <c r="B14" s="5" t="inlineStr">
+      <c r="B14" s="6" t="inlineStr">
         <is>
           <t>リアガラス</t>
         </is>
       </c>
-      <c r="C14" s="5" t="inlineStr">
+      <c r="C14" s="6" t="inlineStr">
         <is>
           <t>パネルなし</t>
         </is>
       </c>
-      <c r="D14" s="5" t="inlineStr">
+      <c r="D14" s="6" t="inlineStr">
         <is>
           <t>白</t>
         </is>
       </c>
-      <c r="E14" s="5" t="inlineStr">
+      <c r="E14" s="6" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -1007,29 +1058,30 @@
           <t>✓</t>
         </is>
       </c>
+      <c r="H14" s="5" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="5" t="inlineStr">
+      <c r="A15" s="6" t="inlineStr">
         <is>
           <t>RAV4</t>
         </is>
       </c>
-      <c r="B15" s="5" t="inlineStr">
+      <c r="B15" s="6" t="inlineStr">
         <is>
           <t>リアガラス</t>
         </is>
       </c>
-      <c r="C15" s="5" t="inlineStr">
+      <c r="C15" s="6" t="inlineStr">
         <is>
           <t>パネルあり</t>
         </is>
       </c>
-      <c r="D15" s="5" t="inlineStr">
+      <c r="D15" s="6" t="inlineStr">
         <is>
           <t>白</t>
         </is>
       </c>
-      <c r="E15" s="5" t="inlineStr">
+      <c r="E15" s="6" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -1044,29 +1096,30 @@
           <t>✓</t>
         </is>
       </c>
+      <c r="H15" s="5" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="5" t="inlineStr">
+      <c r="A16" s="6" t="inlineStr">
         <is>
           <t>RAV4</t>
         </is>
       </c>
-      <c r="B16" s="5" t="inlineStr">
+      <c r="B16" s="6" t="inlineStr">
         <is>
           <t>リアガラス</t>
         </is>
       </c>
-      <c r="C16" s="5" t="inlineStr">
+      <c r="C16" s="6" t="inlineStr">
         <is>
           <t>パネルあり</t>
         </is>
       </c>
-      <c r="D16" s="5" t="inlineStr">
+      <c r="D16" s="6" t="inlineStr">
         <is>
           <t>黒</t>
         </is>
       </c>
-      <c r="E16" s="5" t="inlineStr">
+      <c r="E16" s="6" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -1081,29 +1134,30 @@
           <t>✓</t>
         </is>
       </c>
+      <c r="H16" s="5" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="5" t="inlineStr">
+      <c r="A17" s="6" t="inlineStr">
         <is>
           <t>RAV4</t>
         </is>
       </c>
-      <c r="B17" s="5" t="inlineStr">
+      <c r="B17" s="6" t="inlineStr">
         <is>
           <t>リアガラス</t>
         </is>
       </c>
-      <c r="C17" s="5" t="inlineStr">
+      <c r="C17" s="6" t="inlineStr">
         <is>
           <t>パネルあり</t>
         </is>
       </c>
-      <c r="D17" s="5" t="inlineStr">
+      <c r="D17" s="6" t="inlineStr">
         <is>
           <t>カラー1</t>
         </is>
       </c>
-      <c r="E17" s="5" t="inlineStr">
+      <c r="E17" s="6" t="inlineStr">
         <is>
           <t>カーキー</t>
         </is>
@@ -1118,29 +1172,30 @@
           <t>✓</t>
         </is>
       </c>
+      <c r="H17" s="5" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="5" t="inlineStr">
+      <c r="A18" s="6" t="inlineStr">
         <is>
           <t>RAV4</t>
         </is>
       </c>
-      <c r="B18" s="5" t="inlineStr">
+      <c r="B18" s="6" t="inlineStr">
         <is>
           <t>リアガラス</t>
         </is>
       </c>
-      <c r="C18" s="5" t="inlineStr">
+      <c r="C18" s="6" t="inlineStr">
         <is>
           <t>パネルあり</t>
         </is>
       </c>
-      <c r="D18" s="5" t="inlineStr">
+      <c r="D18" s="6" t="inlineStr">
         <is>
           <t>カラー2</t>
         </is>
       </c>
-      <c r="E18" s="5" t="inlineStr">
+      <c r="E18" s="6" t="inlineStr">
         <is>
           <t>レッドマイカ</t>
         </is>
@@ -1155,29 +1210,30 @@
           <t>✓</t>
         </is>
       </c>
+      <c r="H18" s="5" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="6" t="inlineStr">
+      <c r="A19" s="7" t="inlineStr">
         <is>
           <t>RAV4</t>
         </is>
       </c>
-      <c r="B19" s="6" t="inlineStr">
+      <c r="B19" s="7" t="inlineStr">
         <is>
           <t>正面</t>
         </is>
       </c>
-      <c r="C19" s="6" t="inlineStr">
+      <c r="C19" s="7" t="inlineStr">
         <is>
           <t>パネルなし</t>
         </is>
       </c>
-      <c r="D19" s="6" t="inlineStr">
+      <c r="D19" s="7" t="inlineStr">
         <is>
           <t>白</t>
         </is>
       </c>
-      <c r="E19" s="6" t="inlineStr">
+      <c r="E19" s="7" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -1192,29 +1248,30 @@
           <t>✓</t>
         </is>
       </c>
+      <c r="H19" s="5" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="6" t="inlineStr">
+      <c r="A20" s="7" t="inlineStr">
         <is>
           <t>RAV4</t>
         </is>
       </c>
-      <c r="B20" s="6" t="inlineStr">
+      <c r="B20" s="7" t="inlineStr">
         <is>
           <t>正面</t>
         </is>
       </c>
-      <c r="C20" s="6" t="inlineStr">
+      <c r="C20" s="7" t="inlineStr">
         <is>
           <t>パネルなし</t>
         </is>
       </c>
-      <c r="D20" s="6" t="inlineStr">
+      <c r="D20" s="7" t="inlineStr">
         <is>
           <t>黒</t>
         </is>
       </c>
-      <c r="E20" s="6" t="inlineStr">
+      <c r="E20" s="7" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -1229,29 +1286,30 @@
           <t>✓</t>
         </is>
       </c>
+      <c r="H20" s="5" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="6" t="inlineStr">
+      <c r="A21" s="7" t="inlineStr">
         <is>
           <t>RAV4</t>
         </is>
       </c>
-      <c r="B21" s="6" t="inlineStr">
+      <c r="B21" s="7" t="inlineStr">
         <is>
           <t>正面</t>
         </is>
       </c>
-      <c r="C21" s="6" t="inlineStr">
+      <c r="C21" s="7" t="inlineStr">
         <is>
           <t>パネルなし</t>
         </is>
       </c>
-      <c r="D21" s="6" t="inlineStr">
+      <c r="D21" s="7" t="inlineStr">
         <is>
           <t>カラー1</t>
         </is>
       </c>
-      <c r="E21" s="6" t="inlineStr">
+      <c r="E21" s="7" t="inlineStr">
         <is>
           <t>カーキー</t>
         </is>
@@ -1261,30 +1319,35 @@
           <t>RAV4_正面_パネルなし_カラー1_カーキー</t>
         </is>
       </c>
-      <c r="G21" s="4" t="inlineStr"/>
+      <c r="G21" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="H21" s="5" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="6" t="inlineStr">
+      <c r="A22" s="7" t="inlineStr">
         <is>
           <t>RAV4</t>
         </is>
       </c>
-      <c r="B22" s="6" t="inlineStr">
+      <c r="B22" s="7" t="inlineStr">
         <is>
           <t>正面</t>
         </is>
       </c>
-      <c r="C22" s="6" t="inlineStr">
+      <c r="C22" s="7" t="inlineStr">
         <is>
           <t>パネルなし</t>
         </is>
       </c>
-      <c r="D22" s="6" t="inlineStr">
+      <c r="D22" s="7" t="inlineStr">
         <is>
           <t>カラー2</t>
         </is>
       </c>
-      <c r="E22" s="6" t="inlineStr">
+      <c r="E22" s="7" t="inlineStr">
         <is>
           <t>レッドマイカ</t>
         </is>
@@ -1294,30 +1357,35 @@
           <t>RAV4_正面_パネルなし_カラー2_レッドマイカ</t>
         </is>
       </c>
-      <c r="G22" s="4" t="inlineStr"/>
+      <c r="G22" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="H22" s="5" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="6" t="inlineStr">
+      <c r="A23" s="7" t="inlineStr">
         <is>
           <t>RAV4</t>
         </is>
       </c>
-      <c r="B23" s="6" t="inlineStr">
+      <c r="B23" s="7" t="inlineStr">
         <is>
           <t>正面</t>
         </is>
       </c>
-      <c r="C23" s="6" t="inlineStr">
+      <c r="C23" s="7" t="inlineStr">
         <is>
           <t>ボンネット＋ルーフ</t>
         </is>
       </c>
-      <c r="D23" s="6" t="inlineStr">
+      <c r="D23" s="7" t="inlineStr">
         <is>
           <t>白</t>
         </is>
       </c>
-      <c r="E23" s="6" t="inlineStr">
+      <c r="E23" s="7" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -1332,29 +1400,30 @@
           <t>✓</t>
         </is>
       </c>
+      <c r="H23" s="5" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" s="6" t="inlineStr">
+      <c r="A24" s="7" t="inlineStr">
         <is>
           <t>RAV4</t>
         </is>
       </c>
-      <c r="B24" s="6" t="inlineStr">
+      <c r="B24" s="7" t="inlineStr">
         <is>
           <t>正面</t>
         </is>
       </c>
-      <c r="C24" s="6" t="inlineStr">
+      <c r="C24" s="7" t="inlineStr">
         <is>
           <t>ボンネット＋ルーフ</t>
         </is>
       </c>
-      <c r="D24" s="6" t="inlineStr">
+      <c r="D24" s="7" t="inlineStr">
         <is>
           <t>黒</t>
         </is>
       </c>
-      <c r="E24" s="6" t="inlineStr">
+      <c r="E24" s="7" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -1364,30 +1433,35 @@
           <t>RAV4_正面_ボンネット＋ルーフ_黒</t>
         </is>
       </c>
-      <c r="G24" s="4" t="inlineStr"/>
+      <c r="G24" s="8" t="inlineStr">
+        <is>
+          <t>✗ 要作成</t>
+        </is>
+      </c>
+      <c r="H24" s="5" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" s="6" t="inlineStr">
+      <c r="A25" s="7" t="inlineStr">
         <is>
           <t>RAV4</t>
         </is>
       </c>
-      <c r="B25" s="6" t="inlineStr">
+      <c r="B25" s="7" t="inlineStr">
         <is>
           <t>正面</t>
         </is>
       </c>
-      <c r="C25" s="6" t="inlineStr">
+      <c r="C25" s="7" t="inlineStr">
         <is>
           <t>ボンネット＋ルーフ</t>
         </is>
       </c>
-      <c r="D25" s="6" t="inlineStr">
+      <c r="D25" s="7" t="inlineStr">
         <is>
           <t>カラー1</t>
         </is>
       </c>
-      <c r="E25" s="6" t="inlineStr">
+      <c r="E25" s="7" t="inlineStr">
         <is>
           <t>カーキー</t>
         </is>
@@ -1402,29 +1476,30 @@
           <t>✓</t>
         </is>
       </c>
+      <c r="H25" s="5" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="A26" s="6" t="inlineStr">
+      <c r="A26" s="7" t="inlineStr">
         <is>
           <t>RAV4</t>
         </is>
       </c>
-      <c r="B26" s="6" t="inlineStr">
+      <c r="B26" s="7" t="inlineStr">
         <is>
           <t>正面</t>
         </is>
       </c>
-      <c r="C26" s="6" t="inlineStr">
+      <c r="C26" s="7" t="inlineStr">
         <is>
           <t>ボンネット＋ルーフ</t>
         </is>
       </c>
-      <c r="D26" s="6" t="inlineStr">
+      <c r="D26" s="7" t="inlineStr">
         <is>
           <t>カラー2</t>
         </is>
       </c>
-      <c r="E26" s="6" t="inlineStr">
+      <c r="E26" s="7" t="inlineStr">
         <is>
           <t>レッドマイカ</t>
         </is>
@@ -1439,29 +1514,30 @@
           <t>✓</t>
         </is>
       </c>
+      <c r="H26" s="5" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" s="7" t="inlineStr">
+      <c r="A27" s="9" t="inlineStr">
         <is>
           <t>RAV4</t>
         </is>
       </c>
-      <c r="B27" s="7" t="inlineStr">
+      <c r="B27" s="9" t="inlineStr">
         <is>
           <t>真後ろ</t>
         </is>
       </c>
-      <c r="C27" s="7" t="inlineStr">
+      <c r="C27" s="9" t="inlineStr">
         <is>
           <t>パネルなし</t>
         </is>
       </c>
-      <c r="D27" s="7" t="inlineStr">
+      <c r="D27" s="9" t="inlineStr">
         <is>
           <t>白</t>
         </is>
       </c>
-      <c r="E27" s="7" t="inlineStr">
+      <c r="E27" s="9" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -1476,29 +1552,34 @@
           <t>✓</t>
         </is>
       </c>
+      <c r="H27" s="5" t="inlineStr">
+        <is>
+          <t>画像併用可（リアガラスあり／なし共通）</t>
+        </is>
+      </c>
     </row>
     <row r="28">
-      <c r="A28" s="7" t="inlineStr">
+      <c r="A28" s="9" t="inlineStr">
         <is>
           <t>RAV4</t>
         </is>
       </c>
-      <c r="B28" s="7" t="inlineStr">
+      <c r="B28" s="9" t="inlineStr">
         <is>
           <t>真後ろ</t>
         </is>
       </c>
-      <c r="C28" s="7" t="inlineStr">
+      <c r="C28" s="9" t="inlineStr">
         <is>
           <t>パネルなし</t>
         </is>
       </c>
-      <c r="D28" s="7" t="inlineStr">
+      <c r="D28" s="9" t="inlineStr">
         <is>
           <t>黒</t>
         </is>
       </c>
-      <c r="E28" s="7" t="inlineStr">
+      <c r="E28" s="9" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -1508,30 +1589,39 @@
           <t>RAV4_真後ろ_パネルなし_黒</t>
         </is>
       </c>
-      <c r="G28" s="4" t="inlineStr"/>
+      <c r="G28" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="H28" s="5" t="inlineStr">
+        <is>
+          <t>画像併用可（リアガラスあり／なし共通）</t>
+        </is>
+      </c>
     </row>
     <row r="29">
-      <c r="A29" s="7" t="inlineStr">
+      <c r="A29" s="9" t="inlineStr">
         <is>
           <t>RAV4</t>
         </is>
       </c>
-      <c r="B29" s="7" t="inlineStr">
+      <c r="B29" s="9" t="inlineStr">
         <is>
           <t>真後ろ</t>
         </is>
       </c>
-      <c r="C29" s="7" t="inlineStr">
+      <c r="C29" s="9" t="inlineStr">
         <is>
           <t>パネルなし</t>
         </is>
       </c>
-      <c r="D29" s="7" t="inlineStr">
+      <c r="D29" s="9" t="inlineStr">
         <is>
           <t>カラー1</t>
         </is>
       </c>
-      <c r="E29" s="7" t="inlineStr">
+      <c r="E29" s="9" t="inlineStr">
         <is>
           <t>カーキー</t>
         </is>
@@ -1541,30 +1631,39 @@
           <t>RAV4_真後ろ_パネルなし_カラー1_カーキー</t>
         </is>
       </c>
-      <c r="G29" s="4" t="inlineStr"/>
+      <c r="G29" s="4" t="inlineStr">
+        <is>
+          <t>✓ 画像併用</t>
+        </is>
+      </c>
+      <c r="H29" s="5" t="inlineStr">
+        <is>
+          <t>画像併用可（リアガラスあり／なし共通） → RAV4_真後ろ_リアガラスあり_カラー1_カーキー</t>
+        </is>
+      </c>
     </row>
     <row r="30">
-      <c r="A30" s="7" t="inlineStr">
+      <c r="A30" s="9" t="inlineStr">
         <is>
           <t>RAV4</t>
         </is>
       </c>
-      <c r="B30" s="7" t="inlineStr">
+      <c r="B30" s="9" t="inlineStr">
         <is>
           <t>真後ろ</t>
         </is>
       </c>
-      <c r="C30" s="7" t="inlineStr">
+      <c r="C30" s="9" t="inlineStr">
         <is>
           <t>パネルなし</t>
         </is>
       </c>
-      <c r="D30" s="7" t="inlineStr">
+      <c r="D30" s="9" t="inlineStr">
         <is>
           <t>カラー2</t>
         </is>
       </c>
-      <c r="E30" s="7" t="inlineStr">
+      <c r="E30" s="9" t="inlineStr">
         <is>
           <t>レッドマイカ</t>
         </is>
@@ -1574,30 +1673,39 @@
           <t>RAV4_真後ろ_パネルなし_カラー2_レッドマイカ</t>
         </is>
       </c>
-      <c r="G30" s="4" t="inlineStr"/>
+      <c r="G30" s="4" t="inlineStr">
+        <is>
+          <t>✓ 画像併用</t>
+        </is>
+      </c>
+      <c r="H30" s="5" t="inlineStr">
+        <is>
+          <t>画像併用可（リアガラスあり／なし共通） → RAV4_真後ろ_リアガラスあり_カラー2_レッドマイカ</t>
+        </is>
+      </c>
     </row>
     <row r="31">
-      <c r="A31" s="7" t="inlineStr">
+      <c r="A31" s="9" t="inlineStr">
         <is>
           <t>RAV4</t>
         </is>
       </c>
-      <c r="B31" s="7" t="inlineStr">
+      <c r="B31" s="9" t="inlineStr">
         <is>
           <t>真後ろ</t>
         </is>
       </c>
-      <c r="C31" s="7" t="inlineStr">
+      <c r="C31" s="9" t="inlineStr">
         <is>
           <t>リアガラスあり</t>
         </is>
       </c>
-      <c r="D31" s="7" t="inlineStr">
+      <c r="D31" s="9" t="inlineStr">
         <is>
           <t>白</t>
         </is>
       </c>
-      <c r="E31" s="7" t="inlineStr">
+      <c r="E31" s="9" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -1607,30 +1715,39 @@
           <t>RAV4_真後ろ_リアガラスあり_白</t>
         </is>
       </c>
-      <c r="G31" s="4" t="inlineStr"/>
+      <c r="G31" s="4" t="inlineStr">
+        <is>
+          <t>✓ 画像併用</t>
+        </is>
+      </c>
+      <c r="H31" s="5" t="inlineStr">
+        <is>
+          <t>画像併用可（リアガラスあり／なし共通） → RAV4_真後ろ_パネルなし_白</t>
+        </is>
+      </c>
     </row>
     <row r="32">
-      <c r="A32" s="7" t="inlineStr">
+      <c r="A32" s="9" t="inlineStr">
         <is>
           <t>RAV4</t>
         </is>
       </c>
-      <c r="B32" s="7" t="inlineStr">
+      <c r="B32" s="9" t="inlineStr">
         <is>
           <t>真後ろ</t>
         </is>
       </c>
-      <c r="C32" s="7" t="inlineStr">
+      <c r="C32" s="9" t="inlineStr">
         <is>
           <t>リアガラスあり</t>
         </is>
       </c>
-      <c r="D32" s="7" t="inlineStr">
+      <c r="D32" s="9" t="inlineStr">
         <is>
           <t>黒</t>
         </is>
       </c>
-      <c r="E32" s="7" t="inlineStr">
+      <c r="E32" s="9" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -1640,30 +1757,39 @@
           <t>RAV4_真後ろ_リアガラスあり_黒</t>
         </is>
       </c>
-      <c r="G32" s="4" t="inlineStr"/>
+      <c r="G32" s="4" t="inlineStr">
+        <is>
+          <t>✓ 画像併用</t>
+        </is>
+      </c>
+      <c r="H32" s="5" t="inlineStr">
+        <is>
+          <t>画像併用可（リアガラスあり／なし共通） → RAV4_真後ろ_パネルなし_黒</t>
+        </is>
+      </c>
     </row>
     <row r="33">
-      <c r="A33" s="7" t="inlineStr">
+      <c r="A33" s="9" t="inlineStr">
         <is>
           <t>RAV4</t>
         </is>
       </c>
-      <c r="B33" s="7" t="inlineStr">
+      <c r="B33" s="9" t="inlineStr">
         <is>
           <t>真後ろ</t>
         </is>
       </c>
-      <c r="C33" s="7" t="inlineStr">
+      <c r="C33" s="9" t="inlineStr">
         <is>
           <t>リアガラスあり</t>
         </is>
       </c>
-      <c r="D33" s="7" t="inlineStr">
+      <c r="D33" s="9" t="inlineStr">
         <is>
           <t>カラー1</t>
         </is>
       </c>
-      <c r="E33" s="7" t="inlineStr">
+      <c r="E33" s="9" t="inlineStr">
         <is>
           <t>カーキー</t>
         </is>
@@ -1678,29 +1804,34 @@
           <t>✓</t>
         </is>
       </c>
+      <c r="H33" s="5" t="inlineStr">
+        <is>
+          <t>画像併用可（リアガラスあり／なし共通）</t>
+        </is>
+      </c>
     </row>
     <row r="34">
-      <c r="A34" s="7" t="inlineStr">
+      <c r="A34" s="9" t="inlineStr">
         <is>
           <t>RAV4</t>
         </is>
       </c>
-      <c r="B34" s="7" t="inlineStr">
+      <c r="B34" s="9" t="inlineStr">
         <is>
           <t>真後ろ</t>
         </is>
       </c>
-      <c r="C34" s="7" t="inlineStr">
+      <c r="C34" s="9" t="inlineStr">
         <is>
           <t>リアガラスあり</t>
         </is>
       </c>
-      <c r="D34" s="7" t="inlineStr">
+      <c r="D34" s="9" t="inlineStr">
         <is>
           <t>カラー2</t>
         </is>
       </c>
-      <c r="E34" s="7" t="inlineStr">
+      <c r="E34" s="9" t="inlineStr">
         <is>
           <t>レッドマイカ</t>
         </is>
@@ -1713,6 +1844,11 @@
       <c r="G34" s="4" t="inlineStr">
         <is>
           <t>✓</t>
+        </is>
+      </c>
+      <c r="H34" s="5" t="inlineStr">
+        <is>
+          <t>画像併用可（リアガラスあり／なし共通）</t>
         </is>
       </c>
     </row>
@@ -1752,6 +1888,7 @@
           <t>✓</t>
         </is>
       </c>
+      <c r="H35" s="5" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -1784,7 +1921,12 @@
           <t>RX_斜め上_なし_黒</t>
         </is>
       </c>
-      <c r="G36" s="4" t="inlineStr"/>
+      <c r="G36" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="H36" s="5" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -1817,7 +1959,12 @@
           <t>RX_斜め上_なし_カラー1_ソニックカッパー</t>
         </is>
       </c>
-      <c r="G37" s="4" t="inlineStr"/>
+      <c r="G37" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="H37" s="5" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -1850,7 +1997,12 @@
           <t>RX_斜め上_なし_カラー2_ブルーマイカ</t>
         </is>
       </c>
-      <c r="G38" s="4" t="inlineStr"/>
+      <c r="G38" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="H38" s="5" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -1888,6 +2040,7 @@
           <t>✓</t>
         </is>
       </c>
+      <c r="H39" s="5" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -1925,6 +2078,7 @@
           <t>✓</t>
         </is>
       </c>
+      <c r="H40" s="5" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -1962,6 +2116,7 @@
           <t>✓</t>
         </is>
       </c>
+      <c r="H41" s="5" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -1999,6 +2154,7 @@
           <t>✓</t>
         </is>
       </c>
+      <c r="H42" s="5" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -2036,6 +2192,7 @@
           <t>✓</t>
         </is>
       </c>
+      <c r="H43" s="5" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -2073,6 +2230,7 @@
           <t>✓</t>
         </is>
       </c>
+      <c r="H44" s="5" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -2110,6 +2268,7 @@
           <t>✓</t>
         </is>
       </c>
+      <c r="H45" s="5" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -2147,29 +2306,30 @@
           <t>✓</t>
         </is>
       </c>
+      <c r="H46" s="5" t="inlineStr"/>
     </row>
     <row r="47">
-      <c r="A47" s="5" t="inlineStr">
+      <c r="A47" s="6" t="inlineStr">
         <is>
           <t>RX</t>
         </is>
       </c>
-      <c r="B47" s="5" t="inlineStr">
+      <c r="B47" s="6" t="inlineStr">
         <is>
           <t>リアガラス</t>
         </is>
       </c>
-      <c r="C47" s="5" t="inlineStr">
+      <c r="C47" s="6" t="inlineStr">
         <is>
           <t>パネルなし</t>
         </is>
       </c>
-      <c r="D47" s="5" t="inlineStr">
+      <c r="D47" s="6" t="inlineStr">
         <is>
           <t>白</t>
         </is>
       </c>
-      <c r="E47" s="5" t="inlineStr">
+      <c r="E47" s="6" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -2184,29 +2344,30 @@
           <t>✓</t>
         </is>
       </c>
+      <c r="H47" s="5" t="inlineStr"/>
     </row>
     <row r="48">
-      <c r="A48" s="5" t="inlineStr">
+      <c r="A48" s="6" t="inlineStr">
         <is>
           <t>RX</t>
         </is>
       </c>
-      <c r="B48" s="5" t="inlineStr">
+      <c r="B48" s="6" t="inlineStr">
         <is>
           <t>リアガラス</t>
         </is>
       </c>
-      <c r="C48" s="5" t="inlineStr">
+      <c r="C48" s="6" t="inlineStr">
         <is>
           <t>パネルあり</t>
         </is>
       </c>
-      <c r="D48" s="5" t="inlineStr">
+      <c r="D48" s="6" t="inlineStr">
         <is>
           <t>白</t>
         </is>
       </c>
-      <c r="E48" s="5" t="inlineStr">
+      <c r="E48" s="6" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -2221,29 +2382,30 @@
           <t>✓</t>
         </is>
       </c>
+      <c r="H48" s="5" t="inlineStr"/>
     </row>
     <row r="49">
-      <c r="A49" s="5" t="inlineStr">
+      <c r="A49" s="6" t="inlineStr">
         <is>
           <t>RX</t>
         </is>
       </c>
-      <c r="B49" s="5" t="inlineStr">
+      <c r="B49" s="6" t="inlineStr">
         <is>
           <t>リアガラス</t>
         </is>
       </c>
-      <c r="C49" s="5" t="inlineStr">
+      <c r="C49" s="6" t="inlineStr">
         <is>
           <t>パネルあり</t>
         </is>
       </c>
-      <c r="D49" s="5" t="inlineStr">
+      <c r="D49" s="6" t="inlineStr">
         <is>
           <t>黒</t>
         </is>
       </c>
-      <c r="E49" s="5" t="inlineStr">
+      <c r="E49" s="6" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -2258,29 +2420,30 @@
           <t>✓</t>
         </is>
       </c>
+      <c r="H49" s="5" t="inlineStr"/>
     </row>
     <row r="50">
-      <c r="A50" s="5" t="inlineStr">
+      <c r="A50" s="6" t="inlineStr">
         <is>
           <t>RX</t>
         </is>
       </c>
-      <c r="B50" s="5" t="inlineStr">
+      <c r="B50" s="6" t="inlineStr">
         <is>
           <t>リアガラス</t>
         </is>
       </c>
-      <c r="C50" s="5" t="inlineStr">
+      <c r="C50" s="6" t="inlineStr">
         <is>
           <t>パネルあり</t>
         </is>
       </c>
-      <c r="D50" s="5" t="inlineStr">
+      <c r="D50" s="6" t="inlineStr">
         <is>
           <t>カラー1</t>
         </is>
       </c>
-      <c r="E50" s="5" t="inlineStr">
+      <c r="E50" s="6" t="inlineStr">
         <is>
           <t>ソニックカッパー</t>
         </is>
@@ -2295,29 +2458,30 @@
           <t>✓</t>
         </is>
       </c>
+      <c r="H50" s="5" t="inlineStr"/>
     </row>
     <row r="51">
-      <c r="A51" s="5" t="inlineStr">
+      <c r="A51" s="6" t="inlineStr">
         <is>
           <t>RX</t>
         </is>
       </c>
-      <c r="B51" s="5" t="inlineStr">
+      <c r="B51" s="6" t="inlineStr">
         <is>
           <t>リアガラス</t>
         </is>
       </c>
-      <c r="C51" s="5" t="inlineStr">
+      <c r="C51" s="6" t="inlineStr">
         <is>
           <t>パネルあり</t>
         </is>
       </c>
-      <c r="D51" s="5" t="inlineStr">
+      <c r="D51" s="6" t="inlineStr">
         <is>
           <t>カラー2</t>
         </is>
       </c>
-      <c r="E51" s="5" t="inlineStr">
+      <c r="E51" s="6" t="inlineStr">
         <is>
           <t>ブルーマイカ</t>
         </is>
@@ -2332,29 +2496,30 @@
           <t>✓</t>
         </is>
       </c>
+      <c r="H51" s="5" t="inlineStr"/>
     </row>
     <row r="52">
-      <c r="A52" s="6" t="inlineStr">
+      <c r="A52" s="7" t="inlineStr">
         <is>
           <t>RX</t>
         </is>
       </c>
-      <c r="B52" s="6" t="inlineStr">
+      <c r="B52" s="7" t="inlineStr">
         <is>
           <t>正面</t>
         </is>
       </c>
-      <c r="C52" s="6" t="inlineStr">
+      <c r="C52" s="7" t="inlineStr">
         <is>
           <t>パネルなし</t>
         </is>
       </c>
-      <c r="D52" s="6" t="inlineStr">
+      <c r="D52" s="7" t="inlineStr">
         <is>
           <t>白</t>
         </is>
       </c>
-      <c r="E52" s="6" t="inlineStr">
+      <c r="E52" s="7" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -2369,29 +2534,30 @@
           <t>✓</t>
         </is>
       </c>
+      <c r="H52" s="5" t="inlineStr"/>
     </row>
     <row r="53">
-      <c r="A53" s="6" t="inlineStr">
+      <c r="A53" s="7" t="inlineStr">
         <is>
           <t>RX</t>
         </is>
       </c>
-      <c r="B53" s="6" t="inlineStr">
+      <c r="B53" s="7" t="inlineStr">
         <is>
           <t>正面</t>
         </is>
       </c>
-      <c r="C53" s="6" t="inlineStr">
+      <c r="C53" s="7" t="inlineStr">
         <is>
           <t>パネルなし</t>
         </is>
       </c>
-      <c r="D53" s="6" t="inlineStr">
+      <c r="D53" s="7" t="inlineStr">
         <is>
           <t>黒</t>
         </is>
       </c>
-      <c r="E53" s="6" t="inlineStr">
+      <c r="E53" s="7" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -2401,30 +2567,35 @@
           <t>RX_正面_パネルなし_黒</t>
         </is>
       </c>
-      <c r="G53" s="4" t="inlineStr"/>
+      <c r="G53" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="H53" s="5" t="inlineStr"/>
     </row>
     <row r="54">
-      <c r="A54" s="6" t="inlineStr">
+      <c r="A54" s="7" t="inlineStr">
         <is>
           <t>RX</t>
         </is>
       </c>
-      <c r="B54" s="6" t="inlineStr">
+      <c r="B54" s="7" t="inlineStr">
         <is>
           <t>正面</t>
         </is>
       </c>
-      <c r="C54" s="6" t="inlineStr">
+      <c r="C54" s="7" t="inlineStr">
         <is>
           <t>パネルなし</t>
         </is>
       </c>
-      <c r="D54" s="6" t="inlineStr">
+      <c r="D54" s="7" t="inlineStr">
         <is>
           <t>カラー1</t>
         </is>
       </c>
-      <c r="E54" s="6" t="inlineStr">
+      <c r="E54" s="7" t="inlineStr">
         <is>
           <t>ソニックカッパー</t>
         </is>
@@ -2434,30 +2605,35 @@
           <t>RX_正面_パネルなし_カラー1_ソニックカッパー</t>
         </is>
       </c>
-      <c r="G54" s="4" t="inlineStr"/>
+      <c r="G54" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="H54" s="5" t="inlineStr"/>
     </row>
     <row r="55">
-      <c r="A55" s="6" t="inlineStr">
+      <c r="A55" s="7" t="inlineStr">
         <is>
           <t>RX</t>
         </is>
       </c>
-      <c r="B55" s="6" t="inlineStr">
+      <c r="B55" s="7" t="inlineStr">
         <is>
           <t>正面</t>
         </is>
       </c>
-      <c r="C55" s="6" t="inlineStr">
+      <c r="C55" s="7" t="inlineStr">
         <is>
           <t>パネルなし</t>
         </is>
       </c>
-      <c r="D55" s="6" t="inlineStr">
+      <c r="D55" s="7" t="inlineStr">
         <is>
           <t>カラー2</t>
         </is>
       </c>
-      <c r="E55" s="6" t="inlineStr">
+      <c r="E55" s="7" t="inlineStr">
         <is>
           <t>ブルーマイカ</t>
         </is>
@@ -2467,30 +2643,35 @@
           <t>RX_正面_パネルなし_カラー2_ブルーマイカ</t>
         </is>
       </c>
-      <c r="G55" s="4" t="inlineStr"/>
+      <c r="G55" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="H55" s="5" t="inlineStr"/>
     </row>
     <row r="56">
-      <c r="A56" s="6" t="inlineStr">
+      <c r="A56" s="7" t="inlineStr">
         <is>
           <t>RX</t>
         </is>
       </c>
-      <c r="B56" s="6" t="inlineStr">
+      <c r="B56" s="7" t="inlineStr">
         <is>
           <t>正面</t>
         </is>
       </c>
-      <c r="C56" s="6" t="inlineStr">
+      <c r="C56" s="7" t="inlineStr">
         <is>
           <t>ボンネット＋ルーフ</t>
         </is>
       </c>
-      <c r="D56" s="6" t="inlineStr">
+      <c r="D56" s="7" t="inlineStr">
         <is>
           <t>白</t>
         </is>
       </c>
-      <c r="E56" s="6" t="inlineStr">
+      <c r="E56" s="7" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -2505,29 +2686,30 @@
           <t>✓</t>
         </is>
       </c>
+      <c r="H56" s="5" t="inlineStr"/>
     </row>
     <row r="57">
-      <c r="A57" s="6" t="inlineStr">
+      <c r="A57" s="7" t="inlineStr">
         <is>
           <t>RX</t>
         </is>
       </c>
-      <c r="B57" s="6" t="inlineStr">
+      <c r="B57" s="7" t="inlineStr">
         <is>
           <t>正面</t>
         </is>
       </c>
-      <c r="C57" s="6" t="inlineStr">
+      <c r="C57" s="7" t="inlineStr">
         <is>
           <t>ボンネット＋ルーフ</t>
         </is>
       </c>
-      <c r="D57" s="6" t="inlineStr">
+      <c r="D57" s="7" t="inlineStr">
         <is>
           <t>黒</t>
         </is>
       </c>
-      <c r="E57" s="6" t="inlineStr">
+      <c r="E57" s="7" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -2542,29 +2724,30 @@
           <t>✓</t>
         </is>
       </c>
+      <c r="H57" s="5" t="inlineStr"/>
     </row>
     <row r="58">
-      <c r="A58" s="6" t="inlineStr">
+      <c r="A58" s="7" t="inlineStr">
         <is>
           <t>RX</t>
         </is>
       </c>
-      <c r="B58" s="6" t="inlineStr">
+      <c r="B58" s="7" t="inlineStr">
         <is>
           <t>正面</t>
         </is>
       </c>
-      <c r="C58" s="6" t="inlineStr">
+      <c r="C58" s="7" t="inlineStr">
         <is>
           <t>ボンネット＋ルーフ</t>
         </is>
       </c>
-      <c r="D58" s="6" t="inlineStr">
+      <c r="D58" s="7" t="inlineStr">
         <is>
           <t>カラー1</t>
         </is>
       </c>
-      <c r="E58" s="6" t="inlineStr">
+      <c r="E58" s="7" t="inlineStr">
         <is>
           <t>ソニックカッパー</t>
         </is>
@@ -2579,29 +2762,30 @@
           <t>✓</t>
         </is>
       </c>
+      <c r="H58" s="5" t="inlineStr"/>
     </row>
     <row r="59">
-      <c r="A59" s="6" t="inlineStr">
+      <c r="A59" s="7" t="inlineStr">
         <is>
           <t>RX</t>
         </is>
       </c>
-      <c r="B59" s="6" t="inlineStr">
+      <c r="B59" s="7" t="inlineStr">
         <is>
           <t>正面</t>
         </is>
       </c>
-      <c r="C59" s="6" t="inlineStr">
+      <c r="C59" s="7" t="inlineStr">
         <is>
           <t>ボンネット＋ルーフ</t>
         </is>
       </c>
-      <c r="D59" s="6" t="inlineStr">
+      <c r="D59" s="7" t="inlineStr">
         <is>
           <t>カラー2</t>
         </is>
       </c>
-      <c r="E59" s="6" t="inlineStr">
+      <c r="E59" s="7" t="inlineStr">
         <is>
           <t>ブルーマイカ</t>
         </is>
@@ -2616,29 +2800,30 @@
           <t>✓</t>
         </is>
       </c>
+      <c r="H59" s="5" t="inlineStr"/>
     </row>
     <row r="60">
-      <c r="A60" s="7" t="inlineStr">
+      <c r="A60" s="9" t="inlineStr">
         <is>
           <t>RX</t>
         </is>
       </c>
-      <c r="B60" s="7" t="inlineStr">
+      <c r="B60" s="9" t="inlineStr">
         <is>
           <t>真後ろ</t>
         </is>
       </c>
-      <c r="C60" s="7" t="inlineStr">
+      <c r="C60" s="9" t="inlineStr">
         <is>
           <t>パネルなし</t>
         </is>
       </c>
-      <c r="D60" s="7" t="inlineStr">
+      <c r="D60" s="9" t="inlineStr">
         <is>
           <t>白</t>
         </is>
       </c>
-      <c r="E60" s="7" t="inlineStr">
+      <c r="E60" s="9" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -2653,29 +2838,34 @@
           <t>✓</t>
         </is>
       </c>
+      <c r="H60" s="5" t="inlineStr">
+        <is>
+          <t>画像併用可（リアガラスあり／なし共通）</t>
+        </is>
+      </c>
     </row>
     <row r="61">
-      <c r="A61" s="7" t="inlineStr">
+      <c r="A61" s="9" t="inlineStr">
         <is>
           <t>RX</t>
         </is>
       </c>
-      <c r="B61" s="7" t="inlineStr">
+      <c r="B61" s="9" t="inlineStr">
         <is>
           <t>真後ろ</t>
         </is>
       </c>
-      <c r="C61" s="7" t="inlineStr">
+      <c r="C61" s="9" t="inlineStr">
         <is>
           <t>パネルなし</t>
         </is>
       </c>
-      <c r="D61" s="7" t="inlineStr">
+      <c r="D61" s="9" t="inlineStr">
         <is>
           <t>黒</t>
         </is>
       </c>
-      <c r="E61" s="7" t="inlineStr">
+      <c r="E61" s="9" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -2685,30 +2875,39 @@
           <t>RX_真後ろ_パネルなし_黒</t>
         </is>
       </c>
-      <c r="G61" s="4" t="inlineStr"/>
+      <c r="G61" s="4" t="inlineStr">
+        <is>
+          <t>✓ 画像併用</t>
+        </is>
+      </c>
+      <c r="H61" s="5" t="inlineStr">
+        <is>
+          <t>画像併用可（リアガラスあり／なし共通） → RX_真後ろ_リアガラスあり_黒</t>
+        </is>
+      </c>
     </row>
     <row r="62">
-      <c r="A62" s="7" t="inlineStr">
+      <c r="A62" s="9" t="inlineStr">
         <is>
           <t>RX</t>
         </is>
       </c>
-      <c r="B62" s="7" t="inlineStr">
+      <c r="B62" s="9" t="inlineStr">
         <is>
           <t>真後ろ</t>
         </is>
       </c>
-      <c r="C62" s="7" t="inlineStr">
+      <c r="C62" s="9" t="inlineStr">
         <is>
           <t>パネルなし</t>
         </is>
       </c>
-      <c r="D62" s="7" t="inlineStr">
+      <c r="D62" s="9" t="inlineStr">
         <is>
           <t>カラー1</t>
         </is>
       </c>
-      <c r="E62" s="7" t="inlineStr">
+      <c r="E62" s="9" t="inlineStr">
         <is>
           <t>ソニックカッパー</t>
         </is>
@@ -2718,30 +2917,39 @@
           <t>RX_真後ろ_パネルなし_カラー1_ソニックカッパー</t>
         </is>
       </c>
-      <c r="G62" s="4" t="inlineStr"/>
+      <c r="G62" s="4" t="inlineStr">
+        <is>
+          <t>✓ 画像併用</t>
+        </is>
+      </c>
+      <c r="H62" s="5" t="inlineStr">
+        <is>
+          <t>画像併用可（リアガラスあり／なし共通） → RX_真後ろ_リアガラスあり_カラー1_ソニックカッパー</t>
+        </is>
+      </c>
     </row>
     <row r="63">
-      <c r="A63" s="7" t="inlineStr">
+      <c r="A63" s="9" t="inlineStr">
         <is>
           <t>RX</t>
         </is>
       </c>
-      <c r="B63" s="7" t="inlineStr">
+      <c r="B63" s="9" t="inlineStr">
         <is>
           <t>真後ろ</t>
         </is>
       </c>
-      <c r="C63" s="7" t="inlineStr">
+      <c r="C63" s="9" t="inlineStr">
         <is>
           <t>パネルなし</t>
         </is>
       </c>
-      <c r="D63" s="7" t="inlineStr">
+      <c r="D63" s="9" t="inlineStr">
         <is>
           <t>カラー2</t>
         </is>
       </c>
-      <c r="E63" s="7" t="inlineStr">
+      <c r="E63" s="9" t="inlineStr">
         <is>
           <t>ブルーマイカ</t>
         </is>
@@ -2751,30 +2959,39 @@
           <t>RX_真後ろ_パネルなし_カラー2_ブルーマイカ</t>
         </is>
       </c>
-      <c r="G63" s="4" t="inlineStr"/>
+      <c r="G63" s="4" t="inlineStr">
+        <is>
+          <t>✓ 画像併用</t>
+        </is>
+      </c>
+      <c r="H63" s="5" t="inlineStr">
+        <is>
+          <t>画像併用可（リアガラスあり／なし共通） → RX_真後ろ_リアガラスあり_カラー2_ブルーマイカ</t>
+        </is>
+      </c>
     </row>
     <row r="64">
-      <c r="A64" s="7" t="inlineStr">
+      <c r="A64" s="9" t="inlineStr">
         <is>
           <t>RX</t>
         </is>
       </c>
-      <c r="B64" s="7" t="inlineStr">
+      <c r="B64" s="9" t="inlineStr">
         <is>
           <t>真後ろ</t>
         </is>
       </c>
-      <c r="C64" s="7" t="inlineStr">
+      <c r="C64" s="9" t="inlineStr">
         <is>
           <t>リアガラスあり</t>
         </is>
       </c>
-      <c r="D64" s="7" t="inlineStr">
+      <c r="D64" s="9" t="inlineStr">
         <is>
           <t>白</t>
         </is>
       </c>
-      <c r="E64" s="7" t="inlineStr">
+      <c r="E64" s="9" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -2784,30 +3001,39 @@
           <t>RX_真後ろ_リアガラスあり_白</t>
         </is>
       </c>
-      <c r="G64" s="4" t="inlineStr"/>
+      <c r="G64" s="4" t="inlineStr">
+        <is>
+          <t>✓ 画像併用</t>
+        </is>
+      </c>
+      <c r="H64" s="5" t="inlineStr">
+        <is>
+          <t>画像併用可（リアガラスあり／なし共通） → RX_真後ろ_パネルなし_白</t>
+        </is>
+      </c>
     </row>
     <row r="65">
-      <c r="A65" s="7" t="inlineStr">
+      <c r="A65" s="9" t="inlineStr">
         <is>
           <t>RX</t>
         </is>
       </c>
-      <c r="B65" s="7" t="inlineStr">
+      <c r="B65" s="9" t="inlineStr">
         <is>
           <t>真後ろ</t>
         </is>
       </c>
-      <c r="C65" s="7" t="inlineStr">
+      <c r="C65" s="9" t="inlineStr">
         <is>
           <t>リアガラスあり</t>
         </is>
       </c>
-      <c r="D65" s="7" t="inlineStr">
+      <c r="D65" s="9" t="inlineStr">
         <is>
           <t>黒</t>
         </is>
       </c>
-      <c r="E65" s="7" t="inlineStr">
+      <c r="E65" s="9" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -2822,29 +3048,34 @@
           <t>✓</t>
         </is>
       </c>
+      <c r="H65" s="5" t="inlineStr">
+        <is>
+          <t>画像併用可（リアガラスあり／なし共通）</t>
+        </is>
+      </c>
     </row>
     <row r="66">
-      <c r="A66" s="7" t="inlineStr">
+      <c r="A66" s="9" t="inlineStr">
         <is>
           <t>RX</t>
         </is>
       </c>
-      <c r="B66" s="7" t="inlineStr">
+      <c r="B66" s="9" t="inlineStr">
         <is>
           <t>真後ろ</t>
         </is>
       </c>
-      <c r="C66" s="7" t="inlineStr">
+      <c r="C66" s="9" t="inlineStr">
         <is>
           <t>リアガラスあり</t>
         </is>
       </c>
-      <c r="D66" s="7" t="inlineStr">
+      <c r="D66" s="9" t="inlineStr">
         <is>
           <t>カラー1</t>
         </is>
       </c>
-      <c r="E66" s="7" t="inlineStr">
+      <c r="E66" s="9" t="inlineStr">
         <is>
           <t>ソニックカッパー</t>
         </is>
@@ -2859,29 +3090,34 @@
           <t>✓</t>
         </is>
       </c>
+      <c r="H66" s="5" t="inlineStr">
+        <is>
+          <t>画像併用可（リアガラスあり／なし共通）</t>
+        </is>
+      </c>
     </row>
     <row r="67">
-      <c r="A67" s="7" t="inlineStr">
+      <c r="A67" s="9" t="inlineStr">
         <is>
           <t>RX</t>
         </is>
       </c>
-      <c r="B67" s="7" t="inlineStr">
+      <c r="B67" s="9" t="inlineStr">
         <is>
           <t>真後ろ</t>
         </is>
       </c>
-      <c r="C67" s="7" t="inlineStr">
+      <c r="C67" s="9" t="inlineStr">
         <is>
           <t>リアガラスあり</t>
         </is>
       </c>
-      <c r="D67" s="7" t="inlineStr">
+      <c r="D67" s="9" t="inlineStr">
         <is>
           <t>カラー2</t>
         </is>
       </c>
-      <c r="E67" s="7" t="inlineStr">
+      <c r="E67" s="9" t="inlineStr">
         <is>
           <t>ブルーマイカ</t>
         </is>
@@ -2894,6 +3130,11 @@
       <c r="G67" s="4" t="inlineStr">
         <is>
           <t>✓</t>
+        </is>
+      </c>
+      <c r="H67" s="5" t="inlineStr">
+        <is>
+          <t>画像併用可（リアガラスあり／なし共通）</t>
         </is>
       </c>
     </row>
@@ -2933,6 +3174,7 @@
           <t>✓</t>
         </is>
       </c>
+      <c r="H68" s="5" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -2965,7 +3207,12 @@
           <t>サクラ_斜め上_なし_黒</t>
         </is>
       </c>
-      <c r="G69" s="4" t="inlineStr"/>
+      <c r="G69" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="H69" s="5" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -2998,7 +3245,12 @@
           <t>サクラ_斜め上_なし_カラー1_ソルベブルー</t>
         </is>
       </c>
-      <c r="G70" s="4" t="inlineStr"/>
+      <c r="G70" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="H70" s="5" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -3031,7 +3283,12 @@
           <t>サクラ_斜め上_なし_カラー2_スパークリングレッド</t>
         </is>
       </c>
-      <c r="G71" s="4" t="inlineStr"/>
+      <c r="G71" s="8" t="inlineStr">
+        <is>
+          <t>✗ 要作成</t>
+        </is>
+      </c>
+      <c r="H71" s="5" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -3069,6 +3326,7 @@
           <t>✓</t>
         </is>
       </c>
+      <c r="H72" s="5" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -3106,6 +3364,7 @@
           <t>✓</t>
         </is>
       </c>
+      <c r="H73" s="5" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
@@ -3143,6 +3402,7 @@
           <t>✓</t>
         </is>
       </c>
+      <c r="H74" s="5" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -3180,6 +3440,7 @@
           <t>✓</t>
         </is>
       </c>
+      <c r="H75" s="5" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -3217,6 +3478,7 @@
           <t>✓</t>
         </is>
       </c>
+      <c r="H76" s="5" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -3254,6 +3516,7 @@
           <t>✓</t>
         </is>
       </c>
+      <c r="H77" s="5" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -3291,6 +3554,7 @@
           <t>✓</t>
         </is>
       </c>
+      <c r="H78" s="5" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -3328,29 +3592,30 @@
           <t>✓</t>
         </is>
       </c>
+      <c r="H79" s="5" t="inlineStr"/>
     </row>
     <row r="80">
-      <c r="A80" s="5" t="inlineStr">
+      <c r="A80" s="6" t="inlineStr">
         <is>
           <t>サクラ</t>
         </is>
       </c>
-      <c r="B80" s="5" t="inlineStr">
+      <c r="B80" s="6" t="inlineStr">
         <is>
           <t>リアガラス</t>
         </is>
       </c>
-      <c r="C80" s="5" t="inlineStr">
+      <c r="C80" s="6" t="inlineStr">
         <is>
           <t>パネルなし</t>
         </is>
       </c>
-      <c r="D80" s="5" t="inlineStr">
+      <c r="D80" s="6" t="inlineStr">
         <is>
           <t>白</t>
         </is>
       </c>
-      <c r="E80" s="5" t="inlineStr">
+      <c r="E80" s="6" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -3365,29 +3630,30 @@
           <t>✓</t>
         </is>
       </c>
+      <c r="H80" s="5" t="inlineStr"/>
     </row>
     <row r="81">
-      <c r="A81" s="5" t="inlineStr">
+      <c r="A81" s="6" t="inlineStr">
         <is>
           <t>サクラ</t>
         </is>
       </c>
-      <c r="B81" s="5" t="inlineStr">
+      <c r="B81" s="6" t="inlineStr">
         <is>
           <t>リアガラス</t>
         </is>
       </c>
-      <c r="C81" s="5" t="inlineStr">
+      <c r="C81" s="6" t="inlineStr">
         <is>
           <t>パネルあり</t>
         </is>
       </c>
-      <c r="D81" s="5" t="inlineStr">
+      <c r="D81" s="6" t="inlineStr">
         <is>
           <t>白</t>
         </is>
       </c>
-      <c r="E81" s="5" t="inlineStr">
+      <c r="E81" s="6" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -3402,29 +3668,30 @@
           <t>✓</t>
         </is>
       </c>
+      <c r="H81" s="5" t="inlineStr"/>
     </row>
     <row r="82">
-      <c r="A82" s="5" t="inlineStr">
+      <c r="A82" s="6" t="inlineStr">
         <is>
           <t>サクラ</t>
         </is>
       </c>
-      <c r="B82" s="5" t="inlineStr">
+      <c r="B82" s="6" t="inlineStr">
         <is>
           <t>リアガラス</t>
         </is>
       </c>
-      <c r="C82" s="5" t="inlineStr">
+      <c r="C82" s="6" t="inlineStr">
         <is>
           <t>パネルあり</t>
         </is>
       </c>
-      <c r="D82" s="5" t="inlineStr">
+      <c r="D82" s="6" t="inlineStr">
         <is>
           <t>黒</t>
         </is>
       </c>
-      <c r="E82" s="5" t="inlineStr">
+      <c r="E82" s="6" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -3439,29 +3706,30 @@
           <t>✓</t>
         </is>
       </c>
+      <c r="H82" s="5" t="inlineStr"/>
     </row>
     <row r="83">
-      <c r="A83" s="5" t="inlineStr">
+      <c r="A83" s="6" t="inlineStr">
         <is>
           <t>サクラ</t>
         </is>
       </c>
-      <c r="B83" s="5" t="inlineStr">
+      <c r="B83" s="6" t="inlineStr">
         <is>
           <t>リアガラス</t>
         </is>
       </c>
-      <c r="C83" s="5" t="inlineStr">
+      <c r="C83" s="6" t="inlineStr">
         <is>
           <t>パネルあり</t>
         </is>
       </c>
-      <c r="D83" s="5" t="inlineStr">
+      <c r="D83" s="6" t="inlineStr">
         <is>
           <t>カラー1</t>
         </is>
       </c>
-      <c r="E83" s="5" t="inlineStr">
+      <c r="E83" s="6" t="inlineStr">
         <is>
           <t>ソルベブルー</t>
         </is>
@@ -3476,29 +3744,30 @@
           <t>✓</t>
         </is>
       </c>
+      <c r="H83" s="5" t="inlineStr"/>
     </row>
     <row r="84">
-      <c r="A84" s="5" t="inlineStr">
+      <c r="A84" s="6" t="inlineStr">
         <is>
           <t>サクラ</t>
         </is>
       </c>
-      <c r="B84" s="5" t="inlineStr">
+      <c r="B84" s="6" t="inlineStr">
         <is>
           <t>リアガラス</t>
         </is>
       </c>
-      <c r="C84" s="5" t="inlineStr">
+      <c r="C84" s="6" t="inlineStr">
         <is>
           <t>パネルあり</t>
         </is>
       </c>
-      <c r="D84" s="5" t="inlineStr">
+      <c r="D84" s="6" t="inlineStr">
         <is>
           <t>カラー2</t>
         </is>
       </c>
-      <c r="E84" s="5" t="inlineStr">
+      <c r="E84" s="6" t="inlineStr">
         <is>
           <t>スパークリングレッド</t>
         </is>
@@ -3513,29 +3782,30 @@
           <t>✓</t>
         </is>
       </c>
+      <c r="H84" s="5" t="inlineStr"/>
     </row>
     <row r="85">
-      <c r="A85" s="6" t="inlineStr">
+      <c r="A85" s="7" t="inlineStr">
         <is>
           <t>サクラ</t>
         </is>
       </c>
-      <c r="B85" s="6" t="inlineStr">
+      <c r="B85" s="7" t="inlineStr">
         <is>
           <t>正面</t>
         </is>
       </c>
-      <c r="C85" s="6" t="inlineStr">
+      <c r="C85" s="7" t="inlineStr">
         <is>
           <t>パネルなし</t>
         </is>
       </c>
-      <c r="D85" s="6" t="inlineStr">
+      <c r="D85" s="7" t="inlineStr">
         <is>
           <t>白</t>
         </is>
       </c>
-      <c r="E85" s="6" t="inlineStr">
+      <c r="E85" s="7" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -3550,29 +3820,30 @@
           <t>✓</t>
         </is>
       </c>
+      <c r="H85" s="5" t="inlineStr"/>
     </row>
     <row r="86">
-      <c r="A86" s="6" t="inlineStr">
+      <c r="A86" s="7" t="inlineStr">
         <is>
           <t>サクラ</t>
         </is>
       </c>
-      <c r="B86" s="6" t="inlineStr">
+      <c r="B86" s="7" t="inlineStr">
         <is>
           <t>正面</t>
         </is>
       </c>
-      <c r="C86" s="6" t="inlineStr">
+      <c r="C86" s="7" t="inlineStr">
         <is>
           <t>パネルなし</t>
         </is>
       </c>
-      <c r="D86" s="6" t="inlineStr">
+      <c r="D86" s="7" t="inlineStr">
         <is>
           <t>黒</t>
         </is>
       </c>
-      <c r="E86" s="6" t="inlineStr">
+      <c r="E86" s="7" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -3582,30 +3853,35 @@
           <t>サクラ_正面_パネルなし_黒</t>
         </is>
       </c>
-      <c r="G86" s="4" t="inlineStr"/>
+      <c r="G86" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="H86" s="5" t="inlineStr"/>
     </row>
     <row r="87">
-      <c r="A87" s="6" t="inlineStr">
+      <c r="A87" s="7" t="inlineStr">
         <is>
           <t>サクラ</t>
         </is>
       </c>
-      <c r="B87" s="6" t="inlineStr">
+      <c r="B87" s="7" t="inlineStr">
         <is>
           <t>正面</t>
         </is>
       </c>
-      <c r="C87" s="6" t="inlineStr">
+      <c r="C87" s="7" t="inlineStr">
         <is>
           <t>パネルなし</t>
         </is>
       </c>
-      <c r="D87" s="6" t="inlineStr">
+      <c r="D87" s="7" t="inlineStr">
         <is>
           <t>カラー1</t>
         </is>
       </c>
-      <c r="E87" s="6" t="inlineStr">
+      <c r="E87" s="7" t="inlineStr">
         <is>
           <t>ソルベブルー</t>
         </is>
@@ -3615,30 +3891,35 @@
           <t>サクラ_正面_パネルなし_カラー1_ソルベブルー</t>
         </is>
       </c>
-      <c r="G87" s="4" t="inlineStr"/>
+      <c r="G87" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="H87" s="5" t="inlineStr"/>
     </row>
     <row r="88">
-      <c r="A88" s="6" t="inlineStr">
+      <c r="A88" s="7" t="inlineStr">
         <is>
           <t>サクラ</t>
         </is>
       </c>
-      <c r="B88" s="6" t="inlineStr">
+      <c r="B88" s="7" t="inlineStr">
         <is>
           <t>正面</t>
         </is>
       </c>
-      <c r="C88" s="6" t="inlineStr">
+      <c r="C88" s="7" t="inlineStr">
         <is>
           <t>パネルなし</t>
         </is>
       </c>
-      <c r="D88" s="6" t="inlineStr">
+      <c r="D88" s="7" t="inlineStr">
         <is>
           <t>カラー2</t>
         </is>
       </c>
-      <c r="E88" s="6" t="inlineStr">
+      <c r="E88" s="7" t="inlineStr">
         <is>
           <t>スパークリングレッド</t>
         </is>
@@ -3648,30 +3929,35 @@
           <t>サクラ_正面_パネルなし_カラー2_スパークリングレッド</t>
         </is>
       </c>
-      <c r="G88" s="4" t="inlineStr"/>
+      <c r="G88" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="H88" s="5" t="inlineStr"/>
     </row>
     <row r="89">
-      <c r="A89" s="6" t="inlineStr">
+      <c r="A89" s="7" t="inlineStr">
         <is>
           <t>サクラ</t>
         </is>
       </c>
-      <c r="B89" s="6" t="inlineStr">
+      <c r="B89" s="7" t="inlineStr">
         <is>
           <t>正面</t>
         </is>
       </c>
-      <c r="C89" s="6" t="inlineStr">
+      <c r="C89" s="7" t="inlineStr">
         <is>
           <t>ボンネット＋ルーフ</t>
         </is>
       </c>
-      <c r="D89" s="6" t="inlineStr">
+      <c r="D89" s="7" t="inlineStr">
         <is>
           <t>白</t>
         </is>
       </c>
-      <c r="E89" s="6" t="inlineStr">
+      <c r="E89" s="7" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -3686,29 +3972,30 @@
           <t>✓</t>
         </is>
       </c>
+      <c r="H89" s="5" t="inlineStr"/>
     </row>
     <row r="90">
-      <c r="A90" s="6" t="inlineStr">
+      <c r="A90" s="7" t="inlineStr">
         <is>
           <t>サクラ</t>
         </is>
       </c>
-      <c r="B90" s="6" t="inlineStr">
+      <c r="B90" s="7" t="inlineStr">
         <is>
           <t>正面</t>
         </is>
       </c>
-      <c r="C90" s="6" t="inlineStr">
+      <c r="C90" s="7" t="inlineStr">
         <is>
           <t>ボンネット＋ルーフ</t>
         </is>
       </c>
-      <c r="D90" s="6" t="inlineStr">
+      <c r="D90" s="7" t="inlineStr">
         <is>
           <t>黒</t>
         </is>
       </c>
-      <c r="E90" s="6" t="inlineStr">
+      <c r="E90" s="7" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -3723,29 +4010,30 @@
           <t>✓</t>
         </is>
       </c>
+      <c r="H90" s="5" t="inlineStr"/>
     </row>
     <row r="91">
-      <c r="A91" s="6" t="inlineStr">
+      <c r="A91" s="7" t="inlineStr">
         <is>
           <t>サクラ</t>
         </is>
       </c>
-      <c r="B91" s="6" t="inlineStr">
+      <c r="B91" s="7" t="inlineStr">
         <is>
           <t>正面</t>
         </is>
       </c>
-      <c r="C91" s="6" t="inlineStr">
+      <c r="C91" s="7" t="inlineStr">
         <is>
           <t>ボンネット＋ルーフ</t>
         </is>
       </c>
-      <c r="D91" s="6" t="inlineStr">
+      <c r="D91" s="7" t="inlineStr">
         <is>
           <t>カラー1</t>
         </is>
       </c>
-      <c r="E91" s="6" t="inlineStr">
+      <c r="E91" s="7" t="inlineStr">
         <is>
           <t>ソルベブルー</t>
         </is>
@@ -3760,29 +4048,30 @@
           <t>✓</t>
         </is>
       </c>
+      <c r="H91" s="5" t="inlineStr"/>
     </row>
     <row r="92">
-      <c r="A92" s="6" t="inlineStr">
+      <c r="A92" s="7" t="inlineStr">
         <is>
           <t>サクラ</t>
         </is>
       </c>
-      <c r="B92" s="6" t="inlineStr">
+      <c r="B92" s="7" t="inlineStr">
         <is>
           <t>正面</t>
         </is>
       </c>
-      <c r="C92" s="6" t="inlineStr">
+      <c r="C92" s="7" t="inlineStr">
         <is>
           <t>ボンネット＋ルーフ</t>
         </is>
       </c>
-      <c r="D92" s="6" t="inlineStr">
+      <c r="D92" s="7" t="inlineStr">
         <is>
           <t>カラー2</t>
         </is>
       </c>
-      <c r="E92" s="6" t="inlineStr">
+      <c r="E92" s="7" t="inlineStr">
         <is>
           <t>スパークリングレッド</t>
         </is>
@@ -3797,29 +4086,30 @@
           <t>✓</t>
         </is>
       </c>
+      <c r="H92" s="5" t="inlineStr"/>
     </row>
     <row r="93">
-      <c r="A93" s="7" t="inlineStr">
+      <c r="A93" s="9" t="inlineStr">
         <is>
           <t>サクラ</t>
         </is>
       </c>
-      <c r="B93" s="7" t="inlineStr">
+      <c r="B93" s="9" t="inlineStr">
         <is>
           <t>真後ろ</t>
         </is>
       </c>
-      <c r="C93" s="7" t="inlineStr">
+      <c r="C93" s="9" t="inlineStr">
         <is>
           <t>パネルなし</t>
         </is>
       </c>
-      <c r="D93" s="7" t="inlineStr">
+      <c r="D93" s="9" t="inlineStr">
         <is>
           <t>白</t>
         </is>
       </c>
-      <c r="E93" s="7" t="inlineStr">
+      <c r="E93" s="9" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -3831,32 +4121,37 @@
       </c>
       <c r="G93" s="4" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>✓ 画像併用</t>
+        </is>
+      </c>
+      <c r="H93" s="5" t="inlineStr">
+        <is>
+          <t>画像併用可（リアガラスあり／なし共通） → サクラ_真後ろ_リアガラスあり_白</t>
         </is>
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="7" t="inlineStr">
+      <c r="A94" s="9" t="inlineStr">
         <is>
           <t>サクラ</t>
         </is>
       </c>
-      <c r="B94" s="7" t="inlineStr">
+      <c r="B94" s="9" t="inlineStr">
         <is>
           <t>真後ろ</t>
         </is>
       </c>
-      <c r="C94" s="7" t="inlineStr">
+      <c r="C94" s="9" t="inlineStr">
         <is>
           <t>パネルなし</t>
         </is>
       </c>
-      <c r="D94" s="7" t="inlineStr">
+      <c r="D94" s="9" t="inlineStr">
         <is>
           <t>黒</t>
         </is>
       </c>
-      <c r="E94" s="7" t="inlineStr">
+      <c r="E94" s="9" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -3866,30 +4161,39 @@
           <t>サクラ_真後ろ_パネルなし_黒</t>
         </is>
       </c>
-      <c r="G94" s="4" t="inlineStr"/>
+      <c r="G94" s="4" t="inlineStr">
+        <is>
+          <t>✓ 画像併用</t>
+        </is>
+      </c>
+      <c r="H94" s="5" t="inlineStr">
+        <is>
+          <t>画像併用可（リアガラスあり／なし共通） → サクラ_真後ろ_リアガラスあり_黒</t>
+        </is>
+      </c>
     </row>
     <row r="95">
-      <c r="A95" s="7" t="inlineStr">
+      <c r="A95" s="9" t="inlineStr">
         <is>
           <t>サクラ</t>
         </is>
       </c>
-      <c r="B95" s="7" t="inlineStr">
+      <c r="B95" s="9" t="inlineStr">
         <is>
           <t>真後ろ</t>
         </is>
       </c>
-      <c r="C95" s="7" t="inlineStr">
+      <c r="C95" s="9" t="inlineStr">
         <is>
           <t>パネルなし</t>
         </is>
       </c>
-      <c r="D95" s="7" t="inlineStr">
+      <c r="D95" s="9" t="inlineStr">
         <is>
           <t>カラー1</t>
         </is>
       </c>
-      <c r="E95" s="7" t="inlineStr">
+      <c r="E95" s="9" t="inlineStr">
         <is>
           <t>ソルベブルー</t>
         </is>
@@ -3899,30 +4203,39 @@
           <t>サクラ_真後ろ_パネルなし_カラー1_ソルベブルー</t>
         </is>
       </c>
-      <c r="G95" s="4" t="inlineStr"/>
+      <c r="G95" s="4" t="inlineStr">
+        <is>
+          <t>✓ 画像併用</t>
+        </is>
+      </c>
+      <c r="H95" s="5" t="inlineStr">
+        <is>
+          <t>画像併用可（リアガラスあり／なし共通） → サクラ_真後ろ_リアガラスあり_カラー1_ソルベブルー</t>
+        </is>
+      </c>
     </row>
     <row r="96">
-      <c r="A96" s="7" t="inlineStr">
+      <c r="A96" s="9" t="inlineStr">
         <is>
           <t>サクラ</t>
         </is>
       </c>
-      <c r="B96" s="7" t="inlineStr">
+      <c r="B96" s="9" t="inlineStr">
         <is>
           <t>真後ろ</t>
         </is>
       </c>
-      <c r="C96" s="7" t="inlineStr">
+      <c r="C96" s="9" t="inlineStr">
         <is>
           <t>パネルなし</t>
         </is>
       </c>
-      <c r="D96" s="7" t="inlineStr">
+      <c r="D96" s="9" t="inlineStr">
         <is>
           <t>カラー2</t>
         </is>
       </c>
-      <c r="E96" s="7" t="inlineStr">
+      <c r="E96" s="9" t="inlineStr">
         <is>
           <t>スパークリングレッド</t>
         </is>
@@ -3932,30 +4245,39 @@
           <t>サクラ_真後ろ_パネルなし_カラー2_スパークリングレッド</t>
         </is>
       </c>
-      <c r="G96" s="4" t="inlineStr"/>
+      <c r="G96" s="4" t="inlineStr">
+        <is>
+          <t>✓ 画像併用</t>
+        </is>
+      </c>
+      <c r="H96" s="5" t="inlineStr">
+        <is>
+          <t>画像併用可（リアガラスあり／なし共通） → サクラ_真後ろ_リアガラスあり_カラー2_スパークリングレッド</t>
+        </is>
+      </c>
     </row>
     <row r="97">
-      <c r="A97" s="7" t="inlineStr">
+      <c r="A97" s="9" t="inlineStr">
         <is>
           <t>サクラ</t>
         </is>
       </c>
-      <c r="B97" s="7" t="inlineStr">
+      <c r="B97" s="9" t="inlineStr">
         <is>
           <t>真後ろ</t>
         </is>
       </c>
-      <c r="C97" s="7" t="inlineStr">
+      <c r="C97" s="9" t="inlineStr">
         <is>
           <t>リアガラスあり</t>
         </is>
       </c>
-      <c r="D97" s="7" t="inlineStr">
+      <c r="D97" s="9" t="inlineStr">
         <is>
           <t>白</t>
         </is>
       </c>
-      <c r="E97" s="7" t="inlineStr">
+      <c r="E97" s="9" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -3965,30 +4287,39 @@
           <t>サクラ_真後ろ_リアガラスあり_白</t>
         </is>
       </c>
-      <c r="G97" s="4" t="inlineStr"/>
+      <c r="G97" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="H97" s="5" t="inlineStr">
+        <is>
+          <t>画像併用可（リアガラスあり／なし共通）</t>
+        </is>
+      </c>
     </row>
     <row r="98">
-      <c r="A98" s="7" t="inlineStr">
+      <c r="A98" s="9" t="inlineStr">
         <is>
           <t>サクラ</t>
         </is>
       </c>
-      <c r="B98" s="7" t="inlineStr">
+      <c r="B98" s="9" t="inlineStr">
         <is>
           <t>真後ろ</t>
         </is>
       </c>
-      <c r="C98" s="7" t="inlineStr">
+      <c r="C98" s="9" t="inlineStr">
         <is>
           <t>リアガラスあり</t>
         </is>
       </c>
-      <c r="D98" s="7" t="inlineStr">
+      <c r="D98" s="9" t="inlineStr">
         <is>
           <t>黒</t>
         </is>
       </c>
-      <c r="E98" s="7" t="inlineStr">
+      <c r="E98" s="9" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -4003,29 +4334,34 @@
           <t>✓</t>
         </is>
       </c>
+      <c r="H98" s="5" t="inlineStr">
+        <is>
+          <t>画像併用可（リアガラスあり／なし共通）</t>
+        </is>
+      </c>
     </row>
     <row r="99">
-      <c r="A99" s="7" t="inlineStr">
+      <c r="A99" s="9" t="inlineStr">
         <is>
           <t>サクラ</t>
         </is>
       </c>
-      <c r="B99" s="7" t="inlineStr">
+      <c r="B99" s="9" t="inlineStr">
         <is>
           <t>真後ろ</t>
         </is>
       </c>
-      <c r="C99" s="7" t="inlineStr">
+      <c r="C99" s="9" t="inlineStr">
         <is>
           <t>リアガラスあり</t>
         </is>
       </c>
-      <c r="D99" s="7" t="inlineStr">
+      <c r="D99" s="9" t="inlineStr">
         <is>
           <t>カラー1</t>
         </is>
       </c>
-      <c r="E99" s="7" t="inlineStr">
+      <c r="E99" s="9" t="inlineStr">
         <is>
           <t>ソルベブルー</t>
         </is>
@@ -4040,29 +4376,34 @@
           <t>✓</t>
         </is>
       </c>
+      <c r="H99" s="5" t="inlineStr">
+        <is>
+          <t>画像併用可（リアガラスあり／なし共通）</t>
+        </is>
+      </c>
     </row>
     <row r="100">
-      <c r="A100" s="7" t="inlineStr">
+      <c r="A100" s="9" t="inlineStr">
         <is>
           <t>サクラ</t>
         </is>
       </c>
-      <c r="B100" s="7" t="inlineStr">
+      <c r="B100" s="9" t="inlineStr">
         <is>
           <t>真後ろ</t>
         </is>
       </c>
-      <c r="C100" s="7" t="inlineStr">
+      <c r="C100" s="9" t="inlineStr">
         <is>
           <t>リアガラスあり</t>
         </is>
       </c>
-      <c r="D100" s="7" t="inlineStr">
+      <c r="D100" s="9" t="inlineStr">
         <is>
           <t>カラー2</t>
         </is>
       </c>
-      <c r="E100" s="7" t="inlineStr">
+      <c r="E100" s="9" t="inlineStr">
         <is>
           <t>スパークリングレッド</t>
         </is>
@@ -4075,6 +4416,11 @@
       <c r="G100" s="4" t="inlineStr">
         <is>
           <t>✓</t>
+        </is>
+      </c>
+      <c r="H100" s="5" t="inlineStr">
+        <is>
+          <t>画像併用可（リアガラスあり／なし共通）</t>
         </is>
       </c>
     </row>
@@ -4109,7 +4455,12 @@
           <t>プリウス_斜め上_なし_白</t>
         </is>
       </c>
-      <c r="G101" s="4" t="inlineStr"/>
+      <c r="G101" s="8" t="inlineStr">
+        <is>
+          <t>✗ 要作成</t>
+        </is>
+      </c>
+      <c r="H101" s="5" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
@@ -4142,7 +4493,12 @@
           <t>プリウス_斜め上_なし_黒</t>
         </is>
       </c>
-      <c r="G102" s="4" t="inlineStr"/>
+      <c r="G102" s="8" t="inlineStr">
+        <is>
+          <t>✗ 要作成</t>
+        </is>
+      </c>
+      <c r="H102" s="5" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
@@ -4175,7 +4531,12 @@
           <t>プリウス_斜め上_なし_カラー1</t>
         </is>
       </c>
-      <c r="G103" s="4" t="inlineStr"/>
+      <c r="G103" s="8" t="inlineStr">
+        <is>
+          <t>✗ 要作成</t>
+        </is>
+      </c>
+      <c r="H103" s="5" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
@@ -4208,7 +4569,12 @@
           <t>プリウス_斜め上_なし_カラー2</t>
         </is>
       </c>
-      <c r="G104" s="4" t="inlineStr"/>
+      <c r="G104" s="8" t="inlineStr">
+        <is>
+          <t>✗ 要作成</t>
+        </is>
+      </c>
+      <c r="H104" s="5" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
@@ -4241,7 +4607,12 @@
           <t>プリウス_斜め上_ルーフ_白</t>
         </is>
       </c>
-      <c r="G105" s="4" t="inlineStr"/>
+      <c r="G105" s="8" t="inlineStr">
+        <is>
+          <t>✗ 要作成</t>
+        </is>
+      </c>
+      <c r="H105" s="5" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
@@ -4274,7 +4645,12 @@
           <t>プリウス_斜め上_ルーフ_黒</t>
         </is>
       </c>
-      <c r="G106" s="4" t="inlineStr"/>
+      <c r="G106" s="8" t="inlineStr">
+        <is>
+          <t>✗ 要作成</t>
+        </is>
+      </c>
+      <c r="H106" s="5" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
@@ -4307,7 +4683,12 @@
           <t>プリウス_斜め上_ルーフ_カラー1</t>
         </is>
       </c>
-      <c r="G107" s="4" t="inlineStr"/>
+      <c r="G107" s="8" t="inlineStr">
+        <is>
+          <t>✗ 要作成</t>
+        </is>
+      </c>
+      <c r="H107" s="5" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
@@ -4340,7 +4721,12 @@
           <t>プリウス_斜め上_ルーフ_カラー2</t>
         </is>
       </c>
-      <c r="G108" s="4" t="inlineStr"/>
+      <c r="G108" s="8" t="inlineStr">
+        <is>
+          <t>✗ 要作成</t>
+        </is>
+      </c>
+      <c r="H108" s="5" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
@@ -4373,7 +4759,12 @@
           <t>プリウス_斜め上_ルーフ＋ボンネット_白</t>
         </is>
       </c>
-      <c r="G109" s="4" t="inlineStr"/>
+      <c r="G109" s="8" t="inlineStr">
+        <is>
+          <t>✗ 要作成</t>
+        </is>
+      </c>
+      <c r="H109" s="5" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
@@ -4406,7 +4797,12 @@
           <t>プリウス_斜め上_ルーフ＋ボンネット_黒</t>
         </is>
       </c>
-      <c r="G110" s="4" t="inlineStr"/>
+      <c r="G110" s="8" t="inlineStr">
+        <is>
+          <t>✗ 要作成</t>
+        </is>
+      </c>
+      <c r="H110" s="5" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
@@ -4439,7 +4835,12 @@
           <t>プリウス_斜め上_ルーフ＋ボンネット_カラー1</t>
         </is>
       </c>
-      <c r="G111" s="4" t="inlineStr"/>
+      <c r="G111" s="8" t="inlineStr">
+        <is>
+          <t>✗ 要作成</t>
+        </is>
+      </c>
+      <c r="H111" s="5" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
@@ -4472,30 +4873,35 @@
           <t>プリウス_斜め上_ルーフ＋ボンネット_カラー2</t>
         </is>
       </c>
-      <c r="G112" s="4" t="inlineStr"/>
+      <c r="G112" s="8" t="inlineStr">
+        <is>
+          <t>✗ 要作成</t>
+        </is>
+      </c>
+      <c r="H112" s="5" t="inlineStr"/>
     </row>
     <row r="113">
-      <c r="A113" s="5" t="inlineStr">
+      <c r="A113" s="6" t="inlineStr">
         <is>
           <t>プリウス</t>
         </is>
       </c>
-      <c r="B113" s="5" t="inlineStr">
+      <c r="B113" s="6" t="inlineStr">
         <is>
           <t>リアガラス</t>
         </is>
       </c>
-      <c r="C113" s="5" t="inlineStr">
+      <c r="C113" s="6" t="inlineStr">
         <is>
           <t>パネルなし</t>
         </is>
       </c>
-      <c r="D113" s="5" t="inlineStr">
+      <c r="D113" s="6" t="inlineStr">
         <is>
           <t>白</t>
         </is>
       </c>
-      <c r="E113" s="5" t="inlineStr">
+      <c r="E113" s="6" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -4505,30 +4911,35 @@
           <t>プリウス_リアガラス_パネルなし_白</t>
         </is>
       </c>
-      <c r="G113" s="4" t="inlineStr"/>
+      <c r="G113" s="8" t="inlineStr">
+        <is>
+          <t>✗ 要作成</t>
+        </is>
+      </c>
+      <c r="H113" s="5" t="inlineStr"/>
     </row>
     <row r="114">
-      <c r="A114" s="5" t="inlineStr">
+      <c r="A114" s="6" t="inlineStr">
         <is>
           <t>プリウス</t>
         </is>
       </c>
-      <c r="B114" s="5" t="inlineStr">
+      <c r="B114" s="6" t="inlineStr">
         <is>
           <t>リアガラス</t>
         </is>
       </c>
-      <c r="C114" s="5" t="inlineStr">
+      <c r="C114" s="6" t="inlineStr">
         <is>
           <t>パネルあり</t>
         </is>
       </c>
-      <c r="D114" s="5" t="inlineStr">
+      <c r="D114" s="6" t="inlineStr">
         <is>
           <t>白</t>
         </is>
       </c>
-      <c r="E114" s="5" t="inlineStr">
+      <c r="E114" s="6" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -4538,30 +4949,35 @@
           <t>プリウス_リアガラス_パネルあり_白</t>
         </is>
       </c>
-      <c r="G114" s="4" t="inlineStr"/>
+      <c r="G114" s="8" t="inlineStr">
+        <is>
+          <t>✗ 要作成</t>
+        </is>
+      </c>
+      <c r="H114" s="5" t="inlineStr"/>
     </row>
     <row r="115">
-      <c r="A115" s="5" t="inlineStr">
+      <c r="A115" s="6" t="inlineStr">
         <is>
           <t>プリウス</t>
         </is>
       </c>
-      <c r="B115" s="5" t="inlineStr">
+      <c r="B115" s="6" t="inlineStr">
         <is>
           <t>リアガラス</t>
         </is>
       </c>
-      <c r="C115" s="5" t="inlineStr">
+      <c r="C115" s="6" t="inlineStr">
         <is>
           <t>パネルあり</t>
         </is>
       </c>
-      <c r="D115" s="5" t="inlineStr">
+      <c r="D115" s="6" t="inlineStr">
         <is>
           <t>黒</t>
         </is>
       </c>
-      <c r="E115" s="5" t="inlineStr">
+      <c r="E115" s="6" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -4571,30 +4987,35 @@
           <t>プリウス_リアガラス_パネルあり_黒</t>
         </is>
       </c>
-      <c r="G115" s="4" t="inlineStr"/>
+      <c r="G115" s="8" t="inlineStr">
+        <is>
+          <t>✗ 要作成</t>
+        </is>
+      </c>
+      <c r="H115" s="5" t="inlineStr"/>
     </row>
     <row r="116">
-      <c r="A116" s="5" t="inlineStr">
+      <c r="A116" s="6" t="inlineStr">
         <is>
           <t>プリウス</t>
         </is>
       </c>
-      <c r="B116" s="5" t="inlineStr">
+      <c r="B116" s="6" t="inlineStr">
         <is>
           <t>リアガラス</t>
         </is>
       </c>
-      <c r="C116" s="5" t="inlineStr">
+      <c r="C116" s="6" t="inlineStr">
         <is>
           <t>パネルあり</t>
         </is>
       </c>
-      <c r="D116" s="5" t="inlineStr">
+      <c r="D116" s="6" t="inlineStr">
         <is>
           <t>カラー1</t>
         </is>
       </c>
-      <c r="E116" s="5" t="inlineStr">
+      <c r="E116" s="6" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -4604,30 +5025,35 @@
           <t>プリウス_リアガラス_パネルあり_カラー1</t>
         </is>
       </c>
-      <c r="G116" s="4" t="inlineStr"/>
+      <c r="G116" s="8" t="inlineStr">
+        <is>
+          <t>✗ 要作成</t>
+        </is>
+      </c>
+      <c r="H116" s="5" t="inlineStr"/>
     </row>
     <row r="117">
-      <c r="A117" s="5" t="inlineStr">
+      <c r="A117" s="6" t="inlineStr">
         <is>
           <t>プリウス</t>
         </is>
       </c>
-      <c r="B117" s="5" t="inlineStr">
+      <c r="B117" s="6" t="inlineStr">
         <is>
           <t>リアガラス</t>
         </is>
       </c>
-      <c r="C117" s="5" t="inlineStr">
+      <c r="C117" s="6" t="inlineStr">
         <is>
           <t>パネルあり</t>
         </is>
       </c>
-      <c r="D117" s="5" t="inlineStr">
+      <c r="D117" s="6" t="inlineStr">
         <is>
           <t>カラー2</t>
         </is>
       </c>
-      <c r="E117" s="5" t="inlineStr">
+      <c r="E117" s="6" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -4637,30 +5063,35 @@
           <t>プリウス_リアガラス_パネルあり_カラー2</t>
         </is>
       </c>
-      <c r="G117" s="4" t="inlineStr"/>
+      <c r="G117" s="8" t="inlineStr">
+        <is>
+          <t>✗ 要作成</t>
+        </is>
+      </c>
+      <c r="H117" s="5" t="inlineStr"/>
     </row>
     <row r="118">
-      <c r="A118" s="6" t="inlineStr">
+      <c r="A118" s="7" t="inlineStr">
         <is>
           <t>プリウス</t>
         </is>
       </c>
-      <c r="B118" s="6" t="inlineStr">
+      <c r="B118" s="7" t="inlineStr">
         <is>
           <t>正面</t>
         </is>
       </c>
-      <c r="C118" s="6" t="inlineStr">
+      <c r="C118" s="7" t="inlineStr">
         <is>
           <t>パネルなし</t>
         </is>
       </c>
-      <c r="D118" s="6" t="inlineStr">
+      <c r="D118" s="7" t="inlineStr">
         <is>
           <t>白</t>
         </is>
       </c>
-      <c r="E118" s="6" t="inlineStr">
+      <c r="E118" s="7" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -4670,30 +5101,35 @@
           <t>プリウス_正面_パネルなし_白</t>
         </is>
       </c>
-      <c r="G118" s="4" t="inlineStr"/>
+      <c r="G118" s="8" t="inlineStr">
+        <is>
+          <t>✗ 要作成</t>
+        </is>
+      </c>
+      <c r="H118" s="5" t="inlineStr"/>
     </row>
     <row r="119">
-      <c r="A119" s="6" t="inlineStr">
+      <c r="A119" s="7" t="inlineStr">
         <is>
           <t>プリウス</t>
         </is>
       </c>
-      <c r="B119" s="6" t="inlineStr">
+      <c r="B119" s="7" t="inlineStr">
         <is>
           <t>正面</t>
         </is>
       </c>
-      <c r="C119" s="6" t="inlineStr">
+      <c r="C119" s="7" t="inlineStr">
         <is>
           <t>パネルなし</t>
         </is>
       </c>
-      <c r="D119" s="6" t="inlineStr">
+      <c r="D119" s="7" t="inlineStr">
         <is>
           <t>黒</t>
         </is>
       </c>
-      <c r="E119" s="6" t="inlineStr">
+      <c r="E119" s="7" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -4703,30 +5139,35 @@
           <t>プリウス_正面_パネルなし_黒</t>
         </is>
       </c>
-      <c r="G119" s="4" t="inlineStr"/>
+      <c r="G119" s="8" t="inlineStr">
+        <is>
+          <t>✗ 要作成</t>
+        </is>
+      </c>
+      <c r="H119" s="5" t="inlineStr"/>
     </row>
     <row r="120">
-      <c r="A120" s="6" t="inlineStr">
+      <c r="A120" s="7" t="inlineStr">
         <is>
           <t>プリウス</t>
         </is>
       </c>
-      <c r="B120" s="6" t="inlineStr">
+      <c r="B120" s="7" t="inlineStr">
         <is>
           <t>正面</t>
         </is>
       </c>
-      <c r="C120" s="6" t="inlineStr">
+      <c r="C120" s="7" t="inlineStr">
         <is>
           <t>パネルなし</t>
         </is>
       </c>
-      <c r="D120" s="6" t="inlineStr">
+      <c r="D120" s="7" t="inlineStr">
         <is>
           <t>カラー1</t>
         </is>
       </c>
-      <c r="E120" s="6" t="inlineStr">
+      <c r="E120" s="7" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -4736,30 +5177,35 @@
           <t>プリウス_正面_パネルなし_カラー1</t>
         </is>
       </c>
-      <c r="G120" s="4" t="inlineStr"/>
+      <c r="G120" s="8" t="inlineStr">
+        <is>
+          <t>✗ 要作成</t>
+        </is>
+      </c>
+      <c r="H120" s="5" t="inlineStr"/>
     </row>
     <row r="121">
-      <c r="A121" s="6" t="inlineStr">
+      <c r="A121" s="7" t="inlineStr">
         <is>
           <t>プリウス</t>
         </is>
       </c>
-      <c r="B121" s="6" t="inlineStr">
+      <c r="B121" s="7" t="inlineStr">
         <is>
           <t>正面</t>
         </is>
       </c>
-      <c r="C121" s="6" t="inlineStr">
+      <c r="C121" s="7" t="inlineStr">
         <is>
           <t>パネルなし</t>
         </is>
       </c>
-      <c r="D121" s="6" t="inlineStr">
+      <c r="D121" s="7" t="inlineStr">
         <is>
           <t>カラー2</t>
         </is>
       </c>
-      <c r="E121" s="6" t="inlineStr">
+      <c r="E121" s="7" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -4769,30 +5215,35 @@
           <t>プリウス_正面_パネルなし_カラー2</t>
         </is>
       </c>
-      <c r="G121" s="4" t="inlineStr"/>
+      <c r="G121" s="8" t="inlineStr">
+        <is>
+          <t>✗ 要作成</t>
+        </is>
+      </c>
+      <c r="H121" s="5" t="inlineStr"/>
     </row>
     <row r="122">
-      <c r="A122" s="6" t="inlineStr">
+      <c r="A122" s="7" t="inlineStr">
         <is>
           <t>プリウス</t>
         </is>
       </c>
-      <c r="B122" s="6" t="inlineStr">
+      <c r="B122" s="7" t="inlineStr">
         <is>
           <t>正面</t>
         </is>
       </c>
-      <c r="C122" s="6" t="inlineStr">
+      <c r="C122" s="7" t="inlineStr">
         <is>
           <t>ボンネット＋ルーフ</t>
         </is>
       </c>
-      <c r="D122" s="6" t="inlineStr">
+      <c r="D122" s="7" t="inlineStr">
         <is>
           <t>白</t>
         </is>
       </c>
-      <c r="E122" s="6" t="inlineStr">
+      <c r="E122" s="7" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -4802,30 +5253,35 @@
           <t>プリウス_正面_ボンネット＋ルーフ_白</t>
         </is>
       </c>
-      <c r="G122" s="4" t="inlineStr"/>
+      <c r="G122" s="8" t="inlineStr">
+        <is>
+          <t>✗ 要作成</t>
+        </is>
+      </c>
+      <c r="H122" s="5" t="inlineStr"/>
     </row>
     <row r="123">
-      <c r="A123" s="6" t="inlineStr">
+      <c r="A123" s="7" t="inlineStr">
         <is>
           <t>プリウス</t>
         </is>
       </c>
-      <c r="B123" s="6" t="inlineStr">
+      <c r="B123" s="7" t="inlineStr">
         <is>
           <t>正面</t>
         </is>
       </c>
-      <c r="C123" s="6" t="inlineStr">
+      <c r="C123" s="7" t="inlineStr">
         <is>
           <t>ボンネット＋ルーフ</t>
         </is>
       </c>
-      <c r="D123" s="6" t="inlineStr">
+      <c r="D123" s="7" t="inlineStr">
         <is>
           <t>黒</t>
         </is>
       </c>
-      <c r="E123" s="6" t="inlineStr">
+      <c r="E123" s="7" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -4835,30 +5291,35 @@
           <t>プリウス_正面_ボンネット＋ルーフ_黒</t>
         </is>
       </c>
-      <c r="G123" s="4" t="inlineStr"/>
+      <c r="G123" s="8" t="inlineStr">
+        <is>
+          <t>✗ 要作成</t>
+        </is>
+      </c>
+      <c r="H123" s="5" t="inlineStr"/>
     </row>
     <row r="124">
-      <c r="A124" s="6" t="inlineStr">
+      <c r="A124" s="7" t="inlineStr">
         <is>
           <t>プリウス</t>
         </is>
       </c>
-      <c r="B124" s="6" t="inlineStr">
+      <c r="B124" s="7" t="inlineStr">
         <is>
           <t>正面</t>
         </is>
       </c>
-      <c r="C124" s="6" t="inlineStr">
+      <c r="C124" s="7" t="inlineStr">
         <is>
           <t>ボンネット＋ルーフ</t>
         </is>
       </c>
-      <c r="D124" s="6" t="inlineStr">
+      <c r="D124" s="7" t="inlineStr">
         <is>
           <t>カラー1</t>
         </is>
       </c>
-      <c r="E124" s="6" t="inlineStr">
+      <c r="E124" s="7" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -4868,30 +5329,35 @@
           <t>プリウス_正面_ボンネット＋ルーフ_カラー1</t>
         </is>
       </c>
-      <c r="G124" s="4" t="inlineStr"/>
+      <c r="G124" s="8" t="inlineStr">
+        <is>
+          <t>✗ 要作成</t>
+        </is>
+      </c>
+      <c r="H124" s="5" t="inlineStr"/>
     </row>
     <row r="125">
-      <c r="A125" s="6" t="inlineStr">
+      <c r="A125" s="7" t="inlineStr">
         <is>
           <t>プリウス</t>
         </is>
       </c>
-      <c r="B125" s="6" t="inlineStr">
+      <c r="B125" s="7" t="inlineStr">
         <is>
           <t>正面</t>
         </is>
       </c>
-      <c r="C125" s="6" t="inlineStr">
+      <c r="C125" s="7" t="inlineStr">
         <is>
           <t>ボンネット＋ルーフ</t>
         </is>
       </c>
-      <c r="D125" s="6" t="inlineStr">
+      <c r="D125" s="7" t="inlineStr">
         <is>
           <t>カラー2</t>
         </is>
       </c>
-      <c r="E125" s="6" t="inlineStr">
+      <c r="E125" s="7" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -4901,30 +5367,35 @@
           <t>プリウス_正面_ボンネット＋ルーフ_カラー2</t>
         </is>
       </c>
-      <c r="G125" s="4" t="inlineStr"/>
+      <c r="G125" s="8" t="inlineStr">
+        <is>
+          <t>✗ 要作成</t>
+        </is>
+      </c>
+      <c r="H125" s="5" t="inlineStr"/>
     </row>
     <row r="126">
-      <c r="A126" s="7" t="inlineStr">
+      <c r="A126" s="9" t="inlineStr">
         <is>
           <t>プリウス</t>
         </is>
       </c>
-      <c r="B126" s="7" t="inlineStr">
+      <c r="B126" s="9" t="inlineStr">
         <is>
           <t>真後ろ</t>
         </is>
       </c>
-      <c r="C126" s="7" t="inlineStr">
+      <c r="C126" s="9" t="inlineStr">
         <is>
           <t>パネルなし</t>
         </is>
       </c>
-      <c r="D126" s="7" t="inlineStr">
+      <c r="D126" s="9" t="inlineStr">
         <is>
           <t>白</t>
         </is>
       </c>
-      <c r="E126" s="7" t="inlineStr">
+      <c r="E126" s="9" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -4934,30 +5405,39 @@
           <t>プリウス_真後ろ_パネルなし_白</t>
         </is>
       </c>
-      <c r="G126" s="4" t="inlineStr"/>
+      <c r="G126" s="8" t="inlineStr">
+        <is>
+          <t>✗ 要作成</t>
+        </is>
+      </c>
+      <c r="H126" s="5" t="inlineStr">
+        <is>
+          <t>画像併用可（リアガラスあり／なし共通）</t>
+        </is>
+      </c>
     </row>
     <row r="127">
-      <c r="A127" s="7" t="inlineStr">
+      <c r="A127" s="9" t="inlineStr">
         <is>
           <t>プリウス</t>
         </is>
       </c>
-      <c r="B127" s="7" t="inlineStr">
+      <c r="B127" s="9" t="inlineStr">
         <is>
           <t>真後ろ</t>
         </is>
       </c>
-      <c r="C127" s="7" t="inlineStr">
+      <c r="C127" s="9" t="inlineStr">
         <is>
           <t>パネルなし</t>
         </is>
       </c>
-      <c r="D127" s="7" t="inlineStr">
+      <c r="D127" s="9" t="inlineStr">
         <is>
           <t>黒</t>
         </is>
       </c>
-      <c r="E127" s="7" t="inlineStr">
+      <c r="E127" s="9" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -4967,30 +5447,39 @@
           <t>プリウス_真後ろ_パネルなし_黒</t>
         </is>
       </c>
-      <c r="G127" s="4" t="inlineStr"/>
+      <c r="G127" s="8" t="inlineStr">
+        <is>
+          <t>✗ 要作成</t>
+        </is>
+      </c>
+      <c r="H127" s="5" t="inlineStr">
+        <is>
+          <t>画像併用可（リアガラスあり／なし共通）</t>
+        </is>
+      </c>
     </row>
     <row r="128">
-      <c r="A128" s="7" t="inlineStr">
+      <c r="A128" s="9" t="inlineStr">
         <is>
           <t>プリウス</t>
         </is>
       </c>
-      <c r="B128" s="7" t="inlineStr">
+      <c r="B128" s="9" t="inlineStr">
         <is>
           <t>真後ろ</t>
         </is>
       </c>
-      <c r="C128" s="7" t="inlineStr">
+      <c r="C128" s="9" t="inlineStr">
         <is>
           <t>パネルなし</t>
         </is>
       </c>
-      <c r="D128" s="7" t="inlineStr">
+      <c r="D128" s="9" t="inlineStr">
         <is>
           <t>カラー1</t>
         </is>
       </c>
-      <c r="E128" s="7" t="inlineStr">
+      <c r="E128" s="9" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -5000,30 +5489,39 @@
           <t>プリウス_真後ろ_パネルなし_カラー1</t>
         </is>
       </c>
-      <c r="G128" s="4" t="inlineStr"/>
+      <c r="G128" s="8" t="inlineStr">
+        <is>
+          <t>✗ 要作成</t>
+        </is>
+      </c>
+      <c r="H128" s="5" t="inlineStr">
+        <is>
+          <t>画像併用可（リアガラスあり／なし共通）</t>
+        </is>
+      </c>
     </row>
     <row r="129">
-      <c r="A129" s="7" t="inlineStr">
+      <c r="A129" s="9" t="inlineStr">
         <is>
           <t>プリウス</t>
         </is>
       </c>
-      <c r="B129" s="7" t="inlineStr">
+      <c r="B129" s="9" t="inlineStr">
         <is>
           <t>真後ろ</t>
         </is>
       </c>
-      <c r="C129" s="7" t="inlineStr">
+      <c r="C129" s="9" t="inlineStr">
         <is>
           <t>パネルなし</t>
         </is>
       </c>
-      <c r="D129" s="7" t="inlineStr">
+      <c r="D129" s="9" t="inlineStr">
         <is>
           <t>カラー2</t>
         </is>
       </c>
-      <c r="E129" s="7" t="inlineStr">
+      <c r="E129" s="9" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -5033,30 +5531,39 @@
           <t>プリウス_真後ろ_パネルなし_カラー2</t>
         </is>
       </c>
-      <c r="G129" s="4" t="inlineStr"/>
+      <c r="G129" s="8" t="inlineStr">
+        <is>
+          <t>✗ 要作成</t>
+        </is>
+      </c>
+      <c r="H129" s="5" t="inlineStr">
+        <is>
+          <t>画像併用可（リアガラスあり／なし共通）</t>
+        </is>
+      </c>
     </row>
     <row r="130">
-      <c r="A130" s="7" t="inlineStr">
+      <c r="A130" s="9" t="inlineStr">
         <is>
           <t>プリウス</t>
         </is>
       </c>
-      <c r="B130" s="7" t="inlineStr">
+      <c r="B130" s="9" t="inlineStr">
         <is>
           <t>真後ろ</t>
         </is>
       </c>
-      <c r="C130" s="7" t="inlineStr">
+      <c r="C130" s="9" t="inlineStr">
         <is>
           <t>リアガラスあり</t>
         </is>
       </c>
-      <c r="D130" s="7" t="inlineStr">
+      <c r="D130" s="9" t="inlineStr">
         <is>
           <t>白</t>
         </is>
       </c>
-      <c r="E130" s="7" t="inlineStr">
+      <c r="E130" s="9" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -5066,30 +5573,39 @@
           <t>プリウス_真後ろ_リアガラスあり_白</t>
         </is>
       </c>
-      <c r="G130" s="4" t="inlineStr"/>
+      <c r="G130" s="8" t="inlineStr">
+        <is>
+          <t>✗ 要作成</t>
+        </is>
+      </c>
+      <c r="H130" s="5" t="inlineStr">
+        <is>
+          <t>画像併用可（リアガラスあり／なし共通）</t>
+        </is>
+      </c>
     </row>
     <row r="131">
-      <c r="A131" s="7" t="inlineStr">
+      <c r="A131" s="9" t="inlineStr">
         <is>
           <t>プリウス</t>
         </is>
       </c>
-      <c r="B131" s="7" t="inlineStr">
+      <c r="B131" s="9" t="inlineStr">
         <is>
           <t>真後ろ</t>
         </is>
       </c>
-      <c r="C131" s="7" t="inlineStr">
+      <c r="C131" s="9" t="inlineStr">
         <is>
           <t>リアガラスあり</t>
         </is>
       </c>
-      <c r="D131" s="7" t="inlineStr">
+      <c r="D131" s="9" t="inlineStr">
         <is>
           <t>黒</t>
         </is>
       </c>
-      <c r="E131" s="7" t="inlineStr">
+      <c r="E131" s="9" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -5099,30 +5615,39 @@
           <t>プリウス_真後ろ_リアガラスあり_黒</t>
         </is>
       </c>
-      <c r="G131" s="4" t="inlineStr"/>
+      <c r="G131" s="8" t="inlineStr">
+        <is>
+          <t>✗ 要作成</t>
+        </is>
+      </c>
+      <c r="H131" s="5" t="inlineStr">
+        <is>
+          <t>画像併用可（リアガラスあり／なし共通）</t>
+        </is>
+      </c>
     </row>
     <row r="132">
-      <c r="A132" s="7" t="inlineStr">
+      <c r="A132" s="9" t="inlineStr">
         <is>
           <t>プリウス</t>
         </is>
       </c>
-      <c r="B132" s="7" t="inlineStr">
+      <c r="B132" s="9" t="inlineStr">
         <is>
           <t>真後ろ</t>
         </is>
       </c>
-      <c r="C132" s="7" t="inlineStr">
+      <c r="C132" s="9" t="inlineStr">
         <is>
           <t>リアガラスあり</t>
         </is>
       </c>
-      <c r="D132" s="7" t="inlineStr">
+      <c r="D132" s="9" t="inlineStr">
         <is>
           <t>カラー1</t>
         </is>
       </c>
-      <c r="E132" s="7" t="inlineStr">
+      <c r="E132" s="9" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -5132,30 +5657,39 @@
           <t>プリウス_真後ろ_リアガラスあり_カラー1</t>
         </is>
       </c>
-      <c r="G132" s="4" t="inlineStr"/>
+      <c r="G132" s="8" t="inlineStr">
+        <is>
+          <t>✗ 要作成</t>
+        </is>
+      </c>
+      <c r="H132" s="5" t="inlineStr">
+        <is>
+          <t>画像併用可（リアガラスあり／なし共通）</t>
+        </is>
+      </c>
     </row>
     <row r="133">
-      <c r="A133" s="7" t="inlineStr">
+      <c r="A133" s="9" t="inlineStr">
         <is>
           <t>プリウス</t>
         </is>
       </c>
-      <c r="B133" s="7" t="inlineStr">
+      <c r="B133" s="9" t="inlineStr">
         <is>
           <t>真後ろ</t>
         </is>
       </c>
-      <c r="C133" s="7" t="inlineStr">
+      <c r="C133" s="9" t="inlineStr">
         <is>
           <t>リアガラスあり</t>
         </is>
       </c>
-      <c r="D133" s="7" t="inlineStr">
+      <c r="D133" s="9" t="inlineStr">
         <is>
           <t>カラー2</t>
         </is>
       </c>
-      <c r="E133" s="7" t="inlineStr">
+      <c r="E133" s="9" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -5165,7 +5699,16 @@
           <t>プリウス_真後ろ_リアガラスあり_カラー2</t>
         </is>
       </c>
-      <c r="G133" s="4" t="inlineStr"/>
+      <c r="G133" s="8" t="inlineStr">
+        <is>
+          <t>✗ 要作成</t>
+        </is>
+      </c>
+      <c r="H133" s="5" t="inlineStr">
+        <is>
+          <t>画像併用可（リアガラスあり／なし共通）</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/パターン一覧.xlsx
+++ b/パターン一覧.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="6">
+  <fonts count="8">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -35,6 +35,7 @@
     </font>
     <font>
       <name val="Courier New"/>
+      <color rgb="00000000"/>
       <sz val="9"/>
     </font>
     <font>
@@ -47,8 +48,18 @@
       <color rgb="00CC0000"/>
       <sz val="11"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="001E6B2E"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Courier New"/>
+      <color rgb="001E6B2E"/>
+      <sz val="9"/>
+    </font>
   </fonts>
-  <fills count="8">
+  <fills count="10">
     <fill>
       <patternFill/>
     </fill>
@@ -85,6 +96,16 @@
         <fgColor rgb="00FDEDEC"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E6F4EA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D4EDDA"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -112,7 +133,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -136,6 +157,15 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -503,11 +533,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G88"/>
+  <dimension ref="A1:G100"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
     <col width="22" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="22" customWidth="1" min="5" max="5"/>
@@ -1626,150 +1656,150 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="2" t="inlineStr">
-        <is>
-          <t>RX</t>
-        </is>
-      </c>
-      <c r="B31" s="2" t="inlineStr">
-        <is>
-          <t>斜め上</t>
-        </is>
-      </c>
-      <c r="C31" s="2" t="inlineStr">
-        <is>
-          <t>なし</t>
-        </is>
-      </c>
-      <c r="D31" s="2" t="inlineStr">
+      <c r="A31" s="9" t="inlineStr">
+        <is>
+          <t>RAV4</t>
+        </is>
+      </c>
+      <c r="B31" s="9" t="inlineStr">
+        <is>
+          <t>パーツカラー（斜め上）</t>
+        </is>
+      </c>
+      <c r="C31" s="9" t="inlineStr">
+        <is>
+          <t>ルーフ＋ボンネット</t>
+        </is>
+      </c>
+      <c r="D31" s="9" t="inlineStr">
         <is>
           <t>白</t>
         </is>
       </c>
-      <c r="E31" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F31" s="3" t="inlineStr">
-        <is>
-          <t>RX_斜め上_なし_白</t>
-        </is>
-      </c>
-      <c r="G31" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
+      <c r="E31" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F31" s="10" t="inlineStr">
+        <is>
+          <t>RAV4_斜め上_ルーフ＋ボンネット_白_パーツカラー</t>
+        </is>
+      </c>
+      <c r="G31" s="7" t="inlineStr">
+        <is>
+          <t>✗ 要作成</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="2" t="inlineStr">
-        <is>
-          <t>RX</t>
-        </is>
-      </c>
-      <c r="B32" s="2" t="inlineStr">
-        <is>
-          <t>斜め上</t>
-        </is>
-      </c>
-      <c r="C32" s="2" t="inlineStr">
-        <is>
-          <t>なし</t>
-        </is>
-      </c>
-      <c r="D32" s="2" t="inlineStr">
+      <c r="A32" s="9" t="inlineStr">
+        <is>
+          <t>RAV4</t>
+        </is>
+      </c>
+      <c r="B32" s="9" t="inlineStr">
+        <is>
+          <t>パーツカラー（斜め上）</t>
+        </is>
+      </c>
+      <c r="C32" s="9" t="inlineStr">
+        <is>
+          <t>ルーフ＋ボンネット</t>
+        </is>
+      </c>
+      <c r="D32" s="9" t="inlineStr">
         <is>
           <t>黒</t>
         </is>
       </c>
-      <c r="E32" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F32" s="3" t="inlineStr">
-        <is>
-          <t>RX_斜め上_なし_黒</t>
-        </is>
-      </c>
-      <c r="G32" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
+      <c r="E32" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F32" s="10" t="inlineStr">
+        <is>
+          <t>RAV4_斜め上_ルーフ＋ボンネット_黒_パーツカラー</t>
+        </is>
+      </c>
+      <c r="G32" s="7" t="inlineStr">
+        <is>
+          <t>✗ 要作成</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="2" t="inlineStr">
-        <is>
-          <t>RX</t>
-        </is>
-      </c>
-      <c r="B33" s="2" t="inlineStr">
-        <is>
-          <t>斜め上</t>
-        </is>
-      </c>
-      <c r="C33" s="2" t="inlineStr">
-        <is>
-          <t>なし</t>
-        </is>
-      </c>
-      <c r="D33" s="2" t="inlineStr">
-        <is>
-          <t>カラー1</t>
-        </is>
-      </c>
-      <c r="E33" s="2" t="inlineStr">
-        <is>
-          <t>ソニックカッパー</t>
-        </is>
-      </c>
-      <c r="F33" s="3" t="inlineStr">
-        <is>
-          <t>RX_斜め上_なし_カラー1_ソニックカッパー</t>
-        </is>
-      </c>
-      <c r="G33" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
+      <c r="A33" s="11" t="inlineStr">
+        <is>
+          <t>RAV4</t>
+        </is>
+      </c>
+      <c r="B33" s="11" t="inlineStr">
+        <is>
+          <t>パーツカラー（リアガラス）</t>
+        </is>
+      </c>
+      <c r="C33" s="11" t="inlineStr">
+        <is>
+          <t>リアガラス＋ルーフ</t>
+        </is>
+      </c>
+      <c r="D33" s="11" t="inlineStr">
+        <is>
+          <t>白</t>
+        </is>
+      </c>
+      <c r="E33" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F33" s="10" t="inlineStr">
+        <is>
+          <t>RAV4_リアガラス_パーツカラー_白</t>
+        </is>
+      </c>
+      <c r="G33" s="7" t="inlineStr">
+        <is>
+          <t>✗ 要作成</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="2" t="inlineStr">
-        <is>
-          <t>RX</t>
-        </is>
-      </c>
-      <c r="B34" s="2" t="inlineStr">
-        <is>
-          <t>斜め上</t>
-        </is>
-      </c>
-      <c r="C34" s="2" t="inlineStr">
-        <is>
-          <t>なし</t>
-        </is>
-      </c>
-      <c r="D34" s="2" t="inlineStr">
-        <is>
-          <t>カラー2</t>
-        </is>
-      </c>
-      <c r="E34" s="2" t="inlineStr">
-        <is>
-          <t>ブルーマイカ</t>
-        </is>
-      </c>
-      <c r="F34" s="3" t="inlineStr">
-        <is>
-          <t>RX_斜め上_なし_カラー2_ブルーマイカ</t>
-        </is>
-      </c>
-      <c r="G34" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
+      <c r="A34" s="11" t="inlineStr">
+        <is>
+          <t>RAV4</t>
+        </is>
+      </c>
+      <c r="B34" s="11" t="inlineStr">
+        <is>
+          <t>パーツカラー（リアガラス）</t>
+        </is>
+      </c>
+      <c r="C34" s="11" t="inlineStr">
+        <is>
+          <t>リアガラス＋ルーフ</t>
+        </is>
+      </c>
+      <c r="D34" s="11" t="inlineStr">
+        <is>
+          <t>黒</t>
+        </is>
+      </c>
+      <c r="E34" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F34" s="10" t="inlineStr">
+        <is>
+          <t>RAV4_リアガラス_パーツカラー_黒</t>
+        </is>
+      </c>
+      <c r="G34" s="7" t="inlineStr">
+        <is>
+          <t>✗ 要作成</t>
         </is>
       </c>
     </row>
@@ -1786,7 +1816,7 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>ルーフ</t>
+          <t>なし</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
@@ -1801,7 +1831,7 @@
       </c>
       <c r="F35" s="3" t="inlineStr">
         <is>
-          <t>RX_斜め上_ルーフ_白</t>
+          <t>RX_斜め上_なし_白</t>
         </is>
       </c>
       <c r="G35" s="4" t="inlineStr">
@@ -1823,7 +1853,7 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>ルーフ</t>
+          <t>なし</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
@@ -1838,7 +1868,7 @@
       </c>
       <c r="F36" s="3" t="inlineStr">
         <is>
-          <t>RX_斜め上_ルーフ_黒</t>
+          <t>RX_斜め上_なし_黒</t>
         </is>
       </c>
       <c r="G36" s="4" t="inlineStr">
@@ -1860,7 +1890,7 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>ルーフ</t>
+          <t>なし</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
@@ -1875,7 +1905,7 @@
       </c>
       <c r="F37" s="3" t="inlineStr">
         <is>
-          <t>RX_斜め上_ルーフ_カラー1_ソニックカッパー</t>
+          <t>RX_斜め上_なし_カラー1_ソニックカッパー</t>
         </is>
       </c>
       <c r="G37" s="4" t="inlineStr">
@@ -1897,7 +1927,7 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>ルーフ</t>
+          <t>なし</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
@@ -1912,7 +1942,7 @@
       </c>
       <c r="F38" s="3" t="inlineStr">
         <is>
-          <t>RX_斜め上_ルーフ_カラー2_ブルーマイカ</t>
+          <t>RX_斜め上_なし_カラー2_ブルーマイカ</t>
         </is>
       </c>
       <c r="G38" s="4" t="inlineStr">
@@ -1934,7 +1964,7 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>ルーフ＋ボンネット</t>
+          <t>ルーフ</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
@@ -1949,7 +1979,7 @@
       </c>
       <c r="F39" s="3" t="inlineStr">
         <is>
-          <t>RX_斜め上_ルーフ＋ボンネット_白</t>
+          <t>RX_斜め上_ルーフ_白</t>
         </is>
       </c>
       <c r="G39" s="4" t="inlineStr">
@@ -1971,7 +2001,7 @@
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>ルーフ＋ボンネット</t>
+          <t>ルーフ</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
@@ -1986,7 +2016,7 @@
       </c>
       <c r="F40" s="3" t="inlineStr">
         <is>
-          <t>RX_斜め上_ルーフ＋ボンネット_黒</t>
+          <t>RX_斜め上_ルーフ_黒</t>
         </is>
       </c>
       <c r="G40" s="4" t="inlineStr">
@@ -2008,7 +2038,7 @@
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>ルーフ＋ボンネット</t>
+          <t>ルーフ</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
@@ -2023,7 +2053,7 @@
       </c>
       <c r="F41" s="3" t="inlineStr">
         <is>
-          <t>RX_斜め上_ルーフ＋ボンネット_カラー1_ソニックカッパー</t>
+          <t>RX_斜め上_ルーフ_カラー1_ソニックカッパー</t>
         </is>
       </c>
       <c r="G41" s="4" t="inlineStr">
@@ -2045,170 +2075,170 @@
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
+          <t>ルーフ</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>カラー2</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>ブルーマイカ</t>
+        </is>
+      </c>
+      <c r="F42" s="3" t="inlineStr">
+        <is>
+          <t>RX_斜め上_ルーフ_カラー2_ブルーマイカ</t>
+        </is>
+      </c>
+      <c r="G42" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>RX</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>斜め上</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
           <t>ルーフ＋ボンネット</t>
         </is>
       </c>
-      <c r="D42" s="2" t="inlineStr">
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>白</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F43" s="3" t="inlineStr">
+        <is>
+          <t>RX_斜め上_ルーフ＋ボンネット_白</t>
+        </is>
+      </c>
+      <c r="G43" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>RX</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>斜め上</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>ルーフ＋ボンネット</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>黒</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F44" s="3" t="inlineStr">
+        <is>
+          <t>RX_斜め上_ルーフ＋ボンネット_黒</t>
+        </is>
+      </c>
+      <c r="G44" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>RX</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>斜め上</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>ルーフ＋ボンネット</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>カラー1</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>ソニックカッパー</t>
+        </is>
+      </c>
+      <c r="F45" s="3" t="inlineStr">
+        <is>
+          <t>RX_斜め上_ルーフ＋ボンネット_カラー1_ソニックカッパー</t>
+        </is>
+      </c>
+      <c r="G45" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>RX</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>斜め上</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>ルーフ＋ボンネット</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
         <is>
           <t>カラー2</t>
         </is>
       </c>
-      <c r="E42" s="2" t="inlineStr">
+      <c r="E46" s="2" t="inlineStr">
         <is>
           <t>ブルーマイカ</t>
         </is>
       </c>
-      <c r="F42" s="3" t="inlineStr">
+      <c r="F46" s="3" t="inlineStr">
         <is>
           <t>RX_斜め上_ルーフ＋ボンネット_カラー2_ブルーマイカ</t>
-        </is>
-      </c>
-      <c r="G42" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="5" t="inlineStr">
-        <is>
-          <t>RX</t>
-        </is>
-      </c>
-      <c r="B43" s="5" t="inlineStr">
-        <is>
-          <t>リアガラス</t>
-        </is>
-      </c>
-      <c r="C43" s="5" t="inlineStr">
-        <is>
-          <t>パネルなし</t>
-        </is>
-      </c>
-      <c r="D43" s="5" t="inlineStr">
-        <is>
-          <t>白</t>
-        </is>
-      </c>
-      <c r="E43" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F43" s="3" t="inlineStr">
-        <is>
-          <t>RX_リアガラス_パネルなし_白</t>
-        </is>
-      </c>
-      <c r="G43" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="5" t="inlineStr">
-        <is>
-          <t>RX</t>
-        </is>
-      </c>
-      <c r="B44" s="5" t="inlineStr">
-        <is>
-          <t>リアガラス</t>
-        </is>
-      </c>
-      <c r="C44" s="5" t="inlineStr">
-        <is>
-          <t>パネルあり</t>
-        </is>
-      </c>
-      <c r="D44" s="5" t="inlineStr">
-        <is>
-          <t>白</t>
-        </is>
-      </c>
-      <c r="E44" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F44" s="3" t="inlineStr">
-        <is>
-          <t>RX_リアガラス_パネルあり_白</t>
-        </is>
-      </c>
-      <c r="G44" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="5" t="inlineStr">
-        <is>
-          <t>RX</t>
-        </is>
-      </c>
-      <c r="B45" s="5" t="inlineStr">
-        <is>
-          <t>リアガラス</t>
-        </is>
-      </c>
-      <c r="C45" s="5" t="inlineStr">
-        <is>
-          <t>パネルあり</t>
-        </is>
-      </c>
-      <c r="D45" s="5" t="inlineStr">
-        <is>
-          <t>黒</t>
-        </is>
-      </c>
-      <c r="E45" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F45" s="3" t="inlineStr">
-        <is>
-          <t>RX_リアガラス_パネルあり_黒</t>
-        </is>
-      </c>
-      <c r="G45" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="5" t="inlineStr">
-        <is>
-          <t>RX</t>
-        </is>
-      </c>
-      <c r="B46" s="5" t="inlineStr">
-        <is>
-          <t>リアガラス</t>
-        </is>
-      </c>
-      <c r="C46" s="5" t="inlineStr">
-        <is>
-          <t>パネルあり</t>
-        </is>
-      </c>
-      <c r="D46" s="5" t="inlineStr">
-        <is>
-          <t>カラー1</t>
-        </is>
-      </c>
-      <c r="E46" s="5" t="inlineStr">
-        <is>
-          <t>ソニックカッパー</t>
-        </is>
-      </c>
-      <c r="F46" s="3" t="inlineStr">
-        <is>
-          <t>RX_リアガラス_パネルあり_カラー1_ソニックカッパー</t>
         </is>
       </c>
       <c r="G46" s="4" t="inlineStr">
@@ -2230,170 +2260,170 @@
       </c>
       <c r="C47" s="5" t="inlineStr">
         <is>
+          <t>パネルなし</t>
+        </is>
+      </c>
+      <c r="D47" s="5" t="inlineStr">
+        <is>
+          <t>白</t>
+        </is>
+      </c>
+      <c r="E47" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F47" s="3" t="inlineStr">
+        <is>
+          <t>RX_リアガラス_パネルなし_白</t>
+        </is>
+      </c>
+      <c r="G47" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="5" t="inlineStr">
+        <is>
+          <t>RX</t>
+        </is>
+      </c>
+      <c r="B48" s="5" t="inlineStr">
+        <is>
+          <t>リアガラス</t>
+        </is>
+      </c>
+      <c r="C48" s="5" t="inlineStr">
+        <is>
           <t>パネルあり</t>
         </is>
       </c>
-      <c r="D47" s="5" t="inlineStr">
+      <c r="D48" s="5" t="inlineStr">
+        <is>
+          <t>白</t>
+        </is>
+      </c>
+      <c r="E48" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F48" s="3" t="inlineStr">
+        <is>
+          <t>RX_リアガラス_パネルあり_白</t>
+        </is>
+      </c>
+      <c r="G48" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="5" t="inlineStr">
+        <is>
+          <t>RX</t>
+        </is>
+      </c>
+      <c r="B49" s="5" t="inlineStr">
+        <is>
+          <t>リアガラス</t>
+        </is>
+      </c>
+      <c r="C49" s="5" t="inlineStr">
+        <is>
+          <t>パネルあり</t>
+        </is>
+      </c>
+      <c r="D49" s="5" t="inlineStr">
+        <is>
+          <t>黒</t>
+        </is>
+      </c>
+      <c r="E49" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F49" s="3" t="inlineStr">
+        <is>
+          <t>RX_リアガラス_パネルあり_黒</t>
+        </is>
+      </c>
+      <c r="G49" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="5" t="inlineStr">
+        <is>
+          <t>RX</t>
+        </is>
+      </c>
+      <c r="B50" s="5" t="inlineStr">
+        <is>
+          <t>リアガラス</t>
+        </is>
+      </c>
+      <c r="C50" s="5" t="inlineStr">
+        <is>
+          <t>パネルあり</t>
+        </is>
+      </c>
+      <c r="D50" s="5" t="inlineStr">
+        <is>
+          <t>カラー1</t>
+        </is>
+      </c>
+      <c r="E50" s="5" t="inlineStr">
+        <is>
+          <t>ソニックカッパー</t>
+        </is>
+      </c>
+      <c r="F50" s="3" t="inlineStr">
+        <is>
+          <t>RX_リアガラス_パネルあり_カラー1_ソニックカッパー</t>
+        </is>
+      </c>
+      <c r="G50" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="5" t="inlineStr">
+        <is>
+          <t>RX</t>
+        </is>
+      </c>
+      <c r="B51" s="5" t="inlineStr">
+        <is>
+          <t>リアガラス</t>
+        </is>
+      </c>
+      <c r="C51" s="5" t="inlineStr">
+        <is>
+          <t>パネルあり</t>
+        </is>
+      </c>
+      <c r="D51" s="5" t="inlineStr">
         <is>
           <t>カラー2</t>
         </is>
       </c>
-      <c r="E47" s="5" t="inlineStr">
+      <c r="E51" s="5" t="inlineStr">
         <is>
           <t>ブルーマイカ</t>
         </is>
       </c>
-      <c r="F47" s="3" t="inlineStr">
+      <c r="F51" s="3" t="inlineStr">
         <is>
           <t>RX_リアガラス_パネルあり_カラー2_ブルーマイカ</t>
-        </is>
-      </c>
-      <c r="G47" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="6" t="inlineStr">
-        <is>
-          <t>RX</t>
-        </is>
-      </c>
-      <c r="B48" s="6" t="inlineStr">
-        <is>
-          <t>正面</t>
-        </is>
-      </c>
-      <c r="C48" s="6" t="inlineStr">
-        <is>
-          <t>パネルなし</t>
-        </is>
-      </c>
-      <c r="D48" s="6" t="inlineStr">
-        <is>
-          <t>白</t>
-        </is>
-      </c>
-      <c r="E48" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F48" s="3" t="inlineStr">
-        <is>
-          <t>RX_正面_パネルなし_白</t>
-        </is>
-      </c>
-      <c r="G48" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="6" t="inlineStr">
-        <is>
-          <t>RX</t>
-        </is>
-      </c>
-      <c r="B49" s="6" t="inlineStr">
-        <is>
-          <t>正面</t>
-        </is>
-      </c>
-      <c r="C49" s="6" t="inlineStr">
-        <is>
-          <t>パネルなし</t>
-        </is>
-      </c>
-      <c r="D49" s="6" t="inlineStr">
-        <is>
-          <t>黒</t>
-        </is>
-      </c>
-      <c r="E49" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F49" s="3" t="inlineStr">
-        <is>
-          <t>RX_正面_パネルなし_黒</t>
-        </is>
-      </c>
-      <c r="G49" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="6" t="inlineStr">
-        <is>
-          <t>RX</t>
-        </is>
-      </c>
-      <c r="B50" s="6" t="inlineStr">
-        <is>
-          <t>正面</t>
-        </is>
-      </c>
-      <c r="C50" s="6" t="inlineStr">
-        <is>
-          <t>パネルなし</t>
-        </is>
-      </c>
-      <c r="D50" s="6" t="inlineStr">
-        <is>
-          <t>カラー1</t>
-        </is>
-      </c>
-      <c r="E50" s="6" t="inlineStr">
-        <is>
-          <t>ソニックカッパー</t>
-        </is>
-      </c>
-      <c r="F50" s="3" t="inlineStr">
-        <is>
-          <t>RX_正面_パネルなし_カラー1_ソニックカッパー</t>
-        </is>
-      </c>
-      <c r="G50" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="6" t="inlineStr">
-        <is>
-          <t>RX</t>
-        </is>
-      </c>
-      <c r="B51" s="6" t="inlineStr">
-        <is>
-          <t>正面</t>
-        </is>
-      </c>
-      <c r="C51" s="6" t="inlineStr">
-        <is>
-          <t>パネルなし</t>
-        </is>
-      </c>
-      <c r="D51" s="6" t="inlineStr">
-        <is>
-          <t>カラー2</t>
-        </is>
-      </c>
-      <c r="E51" s="6" t="inlineStr">
-        <is>
-          <t>ブルーマイカ</t>
-        </is>
-      </c>
-      <c r="F51" s="3" t="inlineStr">
-        <is>
-          <t>RX_正面_パネルなし_カラー2_ブルーマイカ</t>
         </is>
       </c>
       <c r="G51" s="4" t="inlineStr">
@@ -2415,7 +2445,7 @@
       </c>
       <c r="C52" s="6" t="inlineStr">
         <is>
-          <t>ボンネット＋ルーフ</t>
+          <t>パネルなし</t>
         </is>
       </c>
       <c r="D52" s="6" t="inlineStr">
@@ -2430,7 +2460,7 @@
       </c>
       <c r="F52" s="3" t="inlineStr">
         <is>
-          <t>RX_正面_ボンネット＋ルーフ_白</t>
+          <t>RX_正面_パネルなし_白</t>
         </is>
       </c>
       <c r="G52" s="4" t="inlineStr">
@@ -2452,7 +2482,7 @@
       </c>
       <c r="C53" s="6" t="inlineStr">
         <is>
-          <t>ボンネット＋ルーフ</t>
+          <t>パネルなし</t>
         </is>
       </c>
       <c r="D53" s="6" t="inlineStr">
@@ -2467,7 +2497,7 @@
       </c>
       <c r="F53" s="3" t="inlineStr">
         <is>
-          <t>RX_正面_ボンネット＋ルーフ_黒</t>
+          <t>RX_正面_パネルなし_黒</t>
         </is>
       </c>
       <c r="G53" s="4" t="inlineStr">
@@ -2489,7 +2519,7 @@
       </c>
       <c r="C54" s="6" t="inlineStr">
         <is>
-          <t>ボンネット＋ルーフ</t>
+          <t>パネルなし</t>
         </is>
       </c>
       <c r="D54" s="6" t="inlineStr">
@@ -2504,7 +2534,7 @@
       </c>
       <c r="F54" s="3" t="inlineStr">
         <is>
-          <t>RX_正面_ボンネット＋ルーフ_カラー1_ソニックカッパー</t>
+          <t>RX_正面_パネルなし_カラー1_ソニックカッパー</t>
         </is>
       </c>
       <c r="G54" s="4" t="inlineStr">
@@ -2526,471 +2556,471 @@
       </c>
       <c r="C55" s="6" t="inlineStr">
         <is>
+          <t>パネルなし</t>
+        </is>
+      </c>
+      <c r="D55" s="6" t="inlineStr">
+        <is>
+          <t>カラー2</t>
+        </is>
+      </c>
+      <c r="E55" s="6" t="inlineStr">
+        <is>
+          <t>ブルーマイカ</t>
+        </is>
+      </c>
+      <c r="F55" s="3" t="inlineStr">
+        <is>
+          <t>RX_正面_パネルなし_カラー2_ブルーマイカ</t>
+        </is>
+      </c>
+      <c r="G55" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="6" t="inlineStr">
+        <is>
+          <t>RX</t>
+        </is>
+      </c>
+      <c r="B56" s="6" t="inlineStr">
+        <is>
+          <t>正面</t>
+        </is>
+      </c>
+      <c r="C56" s="6" t="inlineStr">
+        <is>
           <t>ボンネット＋ルーフ</t>
         </is>
       </c>
-      <c r="D55" s="6" t="inlineStr">
+      <c r="D56" s="6" t="inlineStr">
+        <is>
+          <t>白</t>
+        </is>
+      </c>
+      <c r="E56" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F56" s="3" t="inlineStr">
+        <is>
+          <t>RX_正面_ボンネット＋ルーフ_白</t>
+        </is>
+      </c>
+      <c r="G56" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="6" t="inlineStr">
+        <is>
+          <t>RX</t>
+        </is>
+      </c>
+      <c r="B57" s="6" t="inlineStr">
+        <is>
+          <t>正面</t>
+        </is>
+      </c>
+      <c r="C57" s="6" t="inlineStr">
+        <is>
+          <t>ボンネット＋ルーフ</t>
+        </is>
+      </c>
+      <c r="D57" s="6" t="inlineStr">
+        <is>
+          <t>黒</t>
+        </is>
+      </c>
+      <c r="E57" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F57" s="3" t="inlineStr">
+        <is>
+          <t>RX_正面_ボンネット＋ルーフ_黒</t>
+        </is>
+      </c>
+      <c r="G57" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="6" t="inlineStr">
+        <is>
+          <t>RX</t>
+        </is>
+      </c>
+      <c r="B58" s="6" t="inlineStr">
+        <is>
+          <t>正面</t>
+        </is>
+      </c>
+      <c r="C58" s="6" t="inlineStr">
+        <is>
+          <t>ボンネット＋ルーフ</t>
+        </is>
+      </c>
+      <c r="D58" s="6" t="inlineStr">
+        <is>
+          <t>カラー1</t>
+        </is>
+      </c>
+      <c r="E58" s="6" t="inlineStr">
+        <is>
+          <t>ソニックカッパー</t>
+        </is>
+      </c>
+      <c r="F58" s="3" t="inlineStr">
+        <is>
+          <t>RX_正面_ボンネット＋ルーフ_カラー1_ソニックカッパー</t>
+        </is>
+      </c>
+      <c r="G58" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="6" t="inlineStr">
+        <is>
+          <t>RX</t>
+        </is>
+      </c>
+      <c r="B59" s="6" t="inlineStr">
+        <is>
+          <t>正面</t>
+        </is>
+      </c>
+      <c r="C59" s="6" t="inlineStr">
+        <is>
+          <t>ボンネット＋ルーフ</t>
+        </is>
+      </c>
+      <c r="D59" s="6" t="inlineStr">
         <is>
           <t>カラー2</t>
         </is>
       </c>
-      <c r="E55" s="6" t="inlineStr">
+      <c r="E59" s="6" t="inlineStr">
         <is>
           <t>ブルーマイカ</t>
         </is>
       </c>
-      <c r="F55" s="3" t="inlineStr">
+      <c r="F59" s="3" t="inlineStr">
         <is>
           <t>RX_正面_ボンネット＋ルーフ_カラー2_ブルーマイカ</t>
         </is>
       </c>
-      <c r="G55" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="8" t="inlineStr">
+      <c r="G59" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="8" t="inlineStr">
         <is>
           <t>RX</t>
         </is>
       </c>
-      <c r="B56" s="8" t="inlineStr">
+      <c r="B60" s="8" t="inlineStr">
         <is>
           <t>真後ろ</t>
         </is>
       </c>
-      <c r="C56" s="8" t="inlineStr">
+      <c r="C60" s="8" t="inlineStr">
         <is>
           <t>パネル有りなし併用</t>
         </is>
       </c>
-      <c r="D56" s="8" t="inlineStr">
+      <c r="D60" s="8" t="inlineStr">
         <is>
           <t>白</t>
         </is>
       </c>
-      <c r="E56" s="8" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F56" s="3" t="inlineStr">
+      <c r="E60" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F60" s="3" t="inlineStr">
         <is>
           <t>RX_真後ろ_パネル有りなし併用_白</t>
         </is>
       </c>
-      <c r="G56" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="8" t="inlineStr">
+      <c r="G60" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="8" t="inlineStr">
         <is>
           <t>RX</t>
         </is>
       </c>
-      <c r="B57" s="8" t="inlineStr">
+      <c r="B61" s="8" t="inlineStr">
         <is>
           <t>真後ろ</t>
         </is>
       </c>
-      <c r="C57" s="8" t="inlineStr">
+      <c r="C61" s="8" t="inlineStr">
         <is>
           <t>パネル有りなし併用</t>
         </is>
       </c>
-      <c r="D57" s="8" t="inlineStr">
+      <c r="D61" s="8" t="inlineStr">
         <is>
           <t>黒</t>
         </is>
       </c>
-      <c r="E57" s="8" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F57" s="3" t="inlineStr">
+      <c r="E61" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F61" s="3" t="inlineStr">
         <is>
           <t>RX_真後ろ_パネル有りなし併用_黒</t>
         </is>
       </c>
-      <c r="G57" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="8" t="inlineStr">
+      <c r="G61" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="8" t="inlineStr">
         <is>
           <t>RX</t>
         </is>
       </c>
-      <c r="B58" s="8" t="inlineStr">
+      <c r="B62" s="8" t="inlineStr">
         <is>
           <t>真後ろ</t>
         </is>
       </c>
-      <c r="C58" s="8" t="inlineStr">
+      <c r="C62" s="8" t="inlineStr">
         <is>
           <t>パネル有りなし併用</t>
         </is>
       </c>
-      <c r="D58" s="8" t="inlineStr">
+      <c r="D62" s="8" t="inlineStr">
         <is>
           <t>カラー1</t>
         </is>
       </c>
-      <c r="E58" s="8" t="inlineStr">
+      <c r="E62" s="8" t="inlineStr">
         <is>
           <t>ソニックカッパー</t>
         </is>
       </c>
-      <c r="F58" s="3" t="inlineStr">
+      <c r="F62" s="3" t="inlineStr">
         <is>
           <t>RX_真後ろ_パネル有りなし併用_カラー1_ソニックカッパー</t>
         </is>
       </c>
-      <c r="G58" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" s="8" t="inlineStr">
+      <c r="G62" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="8" t="inlineStr">
         <is>
           <t>RX</t>
         </is>
       </c>
-      <c r="B59" s="8" t="inlineStr">
+      <c r="B63" s="8" t="inlineStr">
         <is>
           <t>真後ろ</t>
         </is>
       </c>
-      <c r="C59" s="8" t="inlineStr">
+      <c r="C63" s="8" t="inlineStr">
         <is>
           <t>パネル有りなし併用</t>
         </is>
       </c>
-      <c r="D59" s="8" t="inlineStr">
+      <c r="D63" s="8" t="inlineStr">
         <is>
           <t>カラー2</t>
         </is>
       </c>
-      <c r="E59" s="8" t="inlineStr">
+      <c r="E63" s="8" t="inlineStr">
         <is>
           <t>ブルーマイカ</t>
         </is>
       </c>
-      <c r="F59" s="3" t="inlineStr">
+      <c r="F63" s="3" t="inlineStr">
         <is>
           <t>RX_真後ろ_パネル有りなし併用_カラー2_ブルーマイカ</t>
         </is>
       </c>
-      <c r="G59" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" s="2" t="inlineStr">
-        <is>
-          <t>サクラ</t>
-        </is>
-      </c>
-      <c r="B60" s="2" t="inlineStr">
-        <is>
-          <t>斜め上</t>
-        </is>
-      </c>
-      <c r="C60" s="2" t="inlineStr">
-        <is>
-          <t>なし</t>
-        </is>
-      </c>
-      <c r="D60" s="2" t="inlineStr">
+      <c r="G63" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="9" t="inlineStr">
+        <is>
+          <t>RX</t>
+        </is>
+      </c>
+      <c r="B64" s="9" t="inlineStr">
+        <is>
+          <t>パーツカラー（斜め上）</t>
+        </is>
+      </c>
+      <c r="C64" s="9" t="inlineStr">
+        <is>
+          <t>ルーフ＋ボンネット</t>
+        </is>
+      </c>
+      <c r="D64" s="9" t="inlineStr">
         <is>
           <t>白</t>
         </is>
       </c>
-      <c r="E60" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F60" s="3" t="inlineStr">
-        <is>
-          <t>サクラ_斜め上_なし_白</t>
-        </is>
-      </c>
-      <c r="G60" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" s="2" t="inlineStr">
-        <is>
-          <t>サクラ</t>
-        </is>
-      </c>
-      <c r="B61" s="2" t="inlineStr">
-        <is>
-          <t>斜め上</t>
-        </is>
-      </c>
-      <c r="C61" s="2" t="inlineStr">
-        <is>
-          <t>なし</t>
-        </is>
-      </c>
-      <c r="D61" s="2" t="inlineStr">
+      <c r="E64" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F64" s="10" t="inlineStr">
+        <is>
+          <t>RX_斜め上_ルーフ＋ボンネット_白_パーツカラー</t>
+        </is>
+      </c>
+      <c r="G64" s="7" t="inlineStr">
+        <is>
+          <t>✗ 要作成</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="9" t="inlineStr">
+        <is>
+          <t>RX</t>
+        </is>
+      </c>
+      <c r="B65" s="9" t="inlineStr">
+        <is>
+          <t>パーツカラー（斜め上）</t>
+        </is>
+      </c>
+      <c r="C65" s="9" t="inlineStr">
+        <is>
+          <t>ルーフ＋ボンネット</t>
+        </is>
+      </c>
+      <c r="D65" s="9" t="inlineStr">
         <is>
           <t>黒</t>
         </is>
       </c>
-      <c r="E61" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F61" s="3" t="inlineStr">
-        <is>
-          <t>サクラ_斜め上_なし_黒</t>
-        </is>
-      </c>
-      <c r="G61" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" s="2" t="inlineStr">
-        <is>
-          <t>サクラ</t>
-        </is>
-      </c>
-      <c r="B62" s="2" t="inlineStr">
-        <is>
-          <t>斜め上</t>
-        </is>
-      </c>
-      <c r="C62" s="2" t="inlineStr">
-        <is>
-          <t>なし</t>
-        </is>
-      </c>
-      <c r="D62" s="2" t="inlineStr">
-        <is>
-          <t>カラー1</t>
-        </is>
-      </c>
-      <c r="E62" s="2" t="inlineStr">
-        <is>
-          <t>ソルベブルー</t>
-        </is>
-      </c>
-      <c r="F62" s="3" t="inlineStr">
-        <is>
-          <t>サクラ_斜め上_なし_カラー1_ソルベブルー</t>
-        </is>
-      </c>
-      <c r="G62" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" s="2" t="inlineStr">
-        <is>
-          <t>サクラ</t>
-        </is>
-      </c>
-      <c r="B63" s="2" t="inlineStr">
-        <is>
-          <t>斜め上</t>
-        </is>
-      </c>
-      <c r="C63" s="2" t="inlineStr">
-        <is>
-          <t>なし</t>
-        </is>
-      </c>
-      <c r="D63" s="2" t="inlineStr">
-        <is>
-          <t>カラー2</t>
-        </is>
-      </c>
-      <c r="E63" s="2" t="inlineStr">
-        <is>
-          <t>スパークリングレッド</t>
-        </is>
-      </c>
-      <c r="F63" s="3" t="inlineStr">
-        <is>
-          <t>サクラ_斜め上_なし_カラー2_スパークリングレッド</t>
-        </is>
-      </c>
-      <c r="G63" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" s="2" t="inlineStr">
-        <is>
-          <t>サクラ</t>
-        </is>
-      </c>
-      <c r="B64" s="2" t="inlineStr">
-        <is>
-          <t>斜め上</t>
-        </is>
-      </c>
-      <c r="C64" s="2" t="inlineStr">
-        <is>
-          <t>ルーフ</t>
-        </is>
-      </c>
-      <c r="D64" s="2" t="inlineStr">
+      <c r="E65" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F65" s="10" t="inlineStr">
+        <is>
+          <t>RX_斜め上_ルーフ＋ボンネット_黒_パーツカラー</t>
+        </is>
+      </c>
+      <c r="G65" s="7" t="inlineStr">
+        <is>
+          <t>✗ 要作成</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="11" t="inlineStr">
+        <is>
+          <t>RX</t>
+        </is>
+      </c>
+      <c r="B66" s="11" t="inlineStr">
+        <is>
+          <t>パーツカラー（リアガラス）</t>
+        </is>
+      </c>
+      <c r="C66" s="11" t="inlineStr">
+        <is>
+          <t>リアガラス＋ルーフ</t>
+        </is>
+      </c>
+      <c r="D66" s="11" t="inlineStr">
         <is>
           <t>白</t>
         </is>
       </c>
-      <c r="E64" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F64" s="3" t="inlineStr">
-        <is>
-          <t>サクラ_斜め上_ルーフ_白</t>
-        </is>
-      </c>
-      <c r="G64" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" s="2" t="inlineStr">
-        <is>
-          <t>サクラ</t>
-        </is>
-      </c>
-      <c r="B65" s="2" t="inlineStr">
-        <is>
-          <t>斜め上</t>
-        </is>
-      </c>
-      <c r="C65" s="2" t="inlineStr">
-        <is>
-          <t>ルーフ</t>
-        </is>
-      </c>
-      <c r="D65" s="2" t="inlineStr">
+      <c r="E66" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F66" s="10" t="inlineStr">
+        <is>
+          <t>RX_リアガラス_パーツカラー_白</t>
+        </is>
+      </c>
+      <c r="G66" s="7" t="inlineStr">
+        <is>
+          <t>✗ 要作成</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="11" t="inlineStr">
+        <is>
+          <t>RX</t>
+        </is>
+      </c>
+      <c r="B67" s="11" t="inlineStr">
+        <is>
+          <t>パーツカラー（リアガラス）</t>
+        </is>
+      </c>
+      <c r="C67" s="11" t="inlineStr">
+        <is>
+          <t>リアガラス＋ルーフ</t>
+        </is>
+      </c>
+      <c r="D67" s="11" t="inlineStr">
         <is>
           <t>黒</t>
         </is>
       </c>
-      <c r="E65" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F65" s="3" t="inlineStr">
-        <is>
-          <t>サクラ_斜め上_ルーフ_黒</t>
-        </is>
-      </c>
-      <c r="G65" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" s="2" t="inlineStr">
-        <is>
-          <t>サクラ</t>
-        </is>
-      </c>
-      <c r="B66" s="2" t="inlineStr">
-        <is>
-          <t>斜め上</t>
-        </is>
-      </c>
-      <c r="C66" s="2" t="inlineStr">
-        <is>
-          <t>ルーフ</t>
-        </is>
-      </c>
-      <c r="D66" s="2" t="inlineStr">
-        <is>
-          <t>カラー1</t>
-        </is>
-      </c>
-      <c r="E66" s="2" t="inlineStr">
-        <is>
-          <t>ソルベブルー</t>
-        </is>
-      </c>
-      <c r="F66" s="3" t="inlineStr">
-        <is>
-          <t>サクラ_斜め上_ルーフ_カラー1_ソルベブルー</t>
-        </is>
-      </c>
-      <c r="G66" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" s="2" t="inlineStr">
-        <is>
-          <t>サクラ</t>
-        </is>
-      </c>
-      <c r="B67" s="2" t="inlineStr">
-        <is>
-          <t>斜め上</t>
-        </is>
-      </c>
-      <c r="C67" s="2" t="inlineStr">
-        <is>
-          <t>ルーフ</t>
-        </is>
-      </c>
-      <c r="D67" s="2" t="inlineStr">
-        <is>
-          <t>カラー2</t>
-        </is>
-      </c>
-      <c r="E67" s="2" t="inlineStr">
-        <is>
-          <t>スパークリングレッド</t>
-        </is>
-      </c>
-      <c r="F67" s="3" t="inlineStr">
-        <is>
-          <t>サクラ_斜め上_ルーフ_カラー2_スパークリングレッド</t>
-        </is>
-      </c>
-      <c r="G67" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
+      <c r="E67" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F67" s="10" t="inlineStr">
+        <is>
+          <t>RX_リアガラス_パーツカラー_黒</t>
+        </is>
+      </c>
+      <c r="G67" s="7" t="inlineStr">
+        <is>
+          <t>✗ 要作成</t>
         </is>
       </c>
     </row>
@@ -3007,7 +3037,7 @@
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>ルーフ＋ボンネット</t>
+          <t>なし</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr">
@@ -3022,7 +3052,7 @@
       </c>
       <c r="F68" s="3" t="inlineStr">
         <is>
-          <t>サクラ_斜め上_ルーフ＋ボンネット_白</t>
+          <t>サクラ_斜め上_なし_白</t>
         </is>
       </c>
       <c r="G68" s="4" t="inlineStr">
@@ -3044,7 +3074,7 @@
       </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>ルーフ＋ボンネット</t>
+          <t>なし</t>
         </is>
       </c>
       <c r="D69" s="2" t="inlineStr">
@@ -3059,7 +3089,7 @@
       </c>
       <c r="F69" s="3" t="inlineStr">
         <is>
-          <t>サクラ_斜め上_ルーフ＋ボンネット_黒</t>
+          <t>サクラ_斜め上_なし_黒</t>
         </is>
       </c>
       <c r="G69" s="4" t="inlineStr">
@@ -3081,7 +3111,7 @@
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>ルーフ＋ボンネット</t>
+          <t>なし</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr">
@@ -3096,7 +3126,7 @@
       </c>
       <c r="F70" s="3" t="inlineStr">
         <is>
-          <t>サクラ_斜め上_ルーフ＋ボンネット_カラー1_ソルベブルー</t>
+          <t>サクラ_斜め上_なし_カラー1_ソルベブルー</t>
         </is>
       </c>
       <c r="G70" s="4" t="inlineStr">
@@ -3118,656 +3148,1100 @@
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
+          <t>なし</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
+        <is>
+          <t>カラー2</t>
+        </is>
+      </c>
+      <c r="E71" s="2" t="inlineStr">
+        <is>
+          <t>スパークリングレッド</t>
+        </is>
+      </c>
+      <c r="F71" s="3" t="inlineStr">
+        <is>
+          <t>サクラ_斜め上_なし_カラー2_スパークリングレッド</t>
+        </is>
+      </c>
+      <c r="G71" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
+        <is>
+          <t>サクラ</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>斜め上</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>ルーフ</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
+        <is>
+          <t>白</t>
+        </is>
+      </c>
+      <c r="E72" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F72" s="3" t="inlineStr">
+        <is>
+          <t>サクラ_斜め上_ルーフ_白</t>
+        </is>
+      </c>
+      <c r="G72" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr">
+        <is>
+          <t>サクラ</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>斜め上</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>ルーフ</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
+        <is>
+          <t>黒</t>
+        </is>
+      </c>
+      <c r="E73" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F73" s="3" t="inlineStr">
+        <is>
+          <t>サクラ_斜め上_ルーフ_黒</t>
+        </is>
+      </c>
+      <c r="G73" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr">
+        <is>
+          <t>サクラ</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>斜め上</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>ルーフ</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
+        <is>
+          <t>カラー1</t>
+        </is>
+      </c>
+      <c r="E74" s="2" t="inlineStr">
+        <is>
+          <t>ソルベブルー</t>
+        </is>
+      </c>
+      <c r="F74" s="3" t="inlineStr">
+        <is>
+          <t>サクラ_斜め上_ルーフ_カラー1_ソルベブルー</t>
+        </is>
+      </c>
+      <c r="G74" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr">
+        <is>
+          <t>サクラ</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>斜め上</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>ルーフ</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
+        <is>
+          <t>カラー2</t>
+        </is>
+      </c>
+      <c r="E75" s="2" t="inlineStr">
+        <is>
+          <t>スパークリングレッド</t>
+        </is>
+      </c>
+      <c r="F75" s="3" t="inlineStr">
+        <is>
+          <t>サクラ_斜め上_ルーフ_カラー2_スパークリングレッド</t>
+        </is>
+      </c>
+      <c r="G75" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
+        <is>
+          <t>サクラ</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>斜め上</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
           <t>ルーフ＋ボンネット</t>
         </is>
       </c>
-      <c r="D71" s="2" t="inlineStr">
+      <c r="D76" s="2" t="inlineStr">
+        <is>
+          <t>白</t>
+        </is>
+      </c>
+      <c r="E76" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F76" s="3" t="inlineStr">
+        <is>
+          <t>サクラ_斜め上_ルーフ＋ボンネット_白</t>
+        </is>
+      </c>
+      <c r="G76" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr">
+        <is>
+          <t>サクラ</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>斜め上</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>ルーフ＋ボンネット</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
+        <is>
+          <t>黒</t>
+        </is>
+      </c>
+      <c r="E77" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F77" s="3" t="inlineStr">
+        <is>
+          <t>サクラ_斜め上_ルーフ＋ボンネット_黒</t>
+        </is>
+      </c>
+      <c r="G77" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
+        <is>
+          <t>サクラ</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>斜め上</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>ルーフ＋ボンネット</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
+        <is>
+          <t>カラー1</t>
+        </is>
+      </c>
+      <c r="E78" s="2" t="inlineStr">
+        <is>
+          <t>ソルベブルー</t>
+        </is>
+      </c>
+      <c r="F78" s="3" t="inlineStr">
+        <is>
+          <t>サクラ_斜め上_ルーフ＋ボンネット_カラー1_ソルベブルー</t>
+        </is>
+      </c>
+      <c r="G78" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr">
+        <is>
+          <t>サクラ</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>斜め上</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>ルーフ＋ボンネット</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
         <is>
           <t>カラー2</t>
         </is>
       </c>
-      <c r="E71" s="2" t="inlineStr">
+      <c r="E79" s="2" t="inlineStr">
         <is>
           <t>スパークリングレッド</t>
         </is>
       </c>
-      <c r="F71" s="3" t="inlineStr">
+      <c r="F79" s="3" t="inlineStr">
         <is>
           <t>サクラ_斜め上_ルーフ＋ボンネット_カラー2_スパークリングレッド</t>
         </is>
       </c>
-      <c r="G71" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" s="5" t="inlineStr">
+      <c r="G79" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="5" t="inlineStr">
         <is>
           <t>サクラ</t>
         </is>
       </c>
-      <c r="B72" s="5" t="inlineStr">
+      <c r="B80" s="5" t="inlineStr">
         <is>
           <t>リアガラス</t>
         </is>
       </c>
-      <c r="C72" s="5" t="inlineStr">
+      <c r="C80" s="5" t="inlineStr">
         <is>
           <t>パネルなし</t>
         </is>
       </c>
-      <c r="D72" s="5" t="inlineStr">
+      <c r="D80" s="5" t="inlineStr">
         <is>
           <t>白</t>
         </is>
       </c>
-      <c r="E72" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F72" s="3" t="inlineStr">
+      <c r="E80" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F80" s="3" t="inlineStr">
         <is>
           <t>サクラ_リアガラス_パネルなし_白</t>
         </is>
       </c>
-      <c r="G72" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" s="5" t="inlineStr">
+      <c r="G80" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="5" t="inlineStr">
         <is>
           <t>サクラ</t>
         </is>
       </c>
-      <c r="B73" s="5" t="inlineStr">
+      <c r="B81" s="5" t="inlineStr">
         <is>
           <t>リアガラス</t>
         </is>
       </c>
-      <c r="C73" s="5" t="inlineStr">
+      <c r="C81" s="5" t="inlineStr">
         <is>
           <t>パネルあり</t>
         </is>
       </c>
-      <c r="D73" s="5" t="inlineStr">
+      <c r="D81" s="5" t="inlineStr">
         <is>
           <t>白</t>
         </is>
       </c>
-      <c r="E73" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F73" s="3" t="inlineStr">
+      <c r="E81" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F81" s="3" t="inlineStr">
         <is>
           <t>サクラ_リアガラス_パネルあり_白</t>
         </is>
       </c>
-      <c r="G73" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" s="5" t="inlineStr">
+      <c r="G81" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="5" t="inlineStr">
         <is>
           <t>サクラ</t>
         </is>
       </c>
-      <c r="B74" s="5" t="inlineStr">
+      <c r="B82" s="5" t="inlineStr">
         <is>
           <t>リアガラス</t>
         </is>
       </c>
-      <c r="C74" s="5" t="inlineStr">
+      <c r="C82" s="5" t="inlineStr">
         <is>
           <t>パネルあり</t>
         </is>
       </c>
-      <c r="D74" s="5" t="inlineStr">
+      <c r="D82" s="5" t="inlineStr">
         <is>
           <t>黒</t>
         </is>
       </c>
-      <c r="E74" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F74" s="3" t="inlineStr">
+      <c r="E82" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F82" s="3" t="inlineStr">
         <is>
           <t>サクラ_リアガラス_パネルあり_黒</t>
         </is>
       </c>
-      <c r="G74" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" s="5" t="inlineStr">
+      <c r="G82" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="5" t="inlineStr">
         <is>
           <t>サクラ</t>
         </is>
       </c>
-      <c r="B75" s="5" t="inlineStr">
+      <c r="B83" s="5" t="inlineStr">
         <is>
           <t>リアガラス</t>
         </is>
       </c>
-      <c r="C75" s="5" t="inlineStr">
+      <c r="C83" s="5" t="inlineStr">
         <is>
           <t>パネルあり</t>
         </is>
       </c>
-      <c r="D75" s="5" t="inlineStr">
+      <c r="D83" s="5" t="inlineStr">
         <is>
           <t>カラー1</t>
         </is>
       </c>
-      <c r="E75" s="5" t="inlineStr">
+      <c r="E83" s="5" t="inlineStr">
         <is>
           <t>ソルベブルー</t>
         </is>
       </c>
-      <c r="F75" s="3" t="inlineStr">
+      <c r="F83" s="3" t="inlineStr">
         <is>
           <t>サクラ_リアガラス_パネルあり_カラー1_ソルベブルー</t>
         </is>
       </c>
-      <c r="G75" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" s="5" t="inlineStr">
+      <c r="G83" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="5" t="inlineStr">
         <is>
           <t>サクラ</t>
         </is>
       </c>
-      <c r="B76" s="5" t="inlineStr">
+      <c r="B84" s="5" t="inlineStr">
         <is>
           <t>リアガラス</t>
         </is>
       </c>
-      <c r="C76" s="5" t="inlineStr">
+      <c r="C84" s="5" t="inlineStr">
         <is>
           <t>パネルあり</t>
         </is>
       </c>
-      <c r="D76" s="5" t="inlineStr">
+      <c r="D84" s="5" t="inlineStr">
         <is>
           <t>カラー2</t>
         </is>
       </c>
-      <c r="E76" s="5" t="inlineStr">
+      <c r="E84" s="5" t="inlineStr">
         <is>
           <t>スパークリングレッド</t>
         </is>
       </c>
-      <c r="F76" s="3" t="inlineStr">
+      <c r="F84" s="3" t="inlineStr">
         <is>
           <t>サクラ_リアガラス_パネルあり_カラー2_スパークリングレッド</t>
         </is>
       </c>
-      <c r="G76" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" s="6" t="inlineStr">
+      <c r="G84" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="6" t="inlineStr">
         <is>
           <t>サクラ</t>
         </is>
       </c>
-      <c r="B77" s="6" t="inlineStr">
+      <c r="B85" s="6" t="inlineStr">
         <is>
           <t>正面</t>
         </is>
       </c>
-      <c r="C77" s="6" t="inlineStr">
+      <c r="C85" s="6" t="inlineStr">
         <is>
           <t>パネルなし</t>
         </is>
       </c>
-      <c r="D77" s="6" t="inlineStr">
+      <c r="D85" s="6" t="inlineStr">
         <is>
           <t>白</t>
         </is>
       </c>
-      <c r="E77" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F77" s="3" t="inlineStr">
+      <c r="E85" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F85" s="3" t="inlineStr">
         <is>
           <t>サクラ_正面_パネルなし_白</t>
         </is>
       </c>
-      <c r="G77" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" s="6" t="inlineStr">
+      <c r="G85" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="6" t="inlineStr">
         <is>
           <t>サクラ</t>
         </is>
       </c>
-      <c r="B78" s="6" t="inlineStr">
+      <c r="B86" s="6" t="inlineStr">
         <is>
           <t>正面</t>
         </is>
       </c>
-      <c r="C78" s="6" t="inlineStr">
+      <c r="C86" s="6" t="inlineStr">
         <is>
           <t>パネルなし</t>
         </is>
       </c>
-      <c r="D78" s="6" t="inlineStr">
+      <c r="D86" s="6" t="inlineStr">
         <is>
           <t>黒</t>
         </is>
       </c>
-      <c r="E78" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F78" s="3" t="inlineStr">
+      <c r="E86" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F86" s="3" t="inlineStr">
         <is>
           <t>サクラ_正面_パネルなし_黒</t>
         </is>
       </c>
-      <c r="G78" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" s="6" t="inlineStr">
+      <c r="G86" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="6" t="inlineStr">
         <is>
           <t>サクラ</t>
         </is>
       </c>
-      <c r="B79" s="6" t="inlineStr">
+      <c r="B87" s="6" t="inlineStr">
         <is>
           <t>正面</t>
         </is>
       </c>
-      <c r="C79" s="6" t="inlineStr">
+      <c r="C87" s="6" t="inlineStr">
         <is>
           <t>パネルなし</t>
         </is>
       </c>
-      <c r="D79" s="6" t="inlineStr">
+      <c r="D87" s="6" t="inlineStr">
         <is>
           <t>カラー1</t>
         </is>
       </c>
-      <c r="E79" s="6" t="inlineStr">
+      <c r="E87" s="6" t="inlineStr">
         <is>
           <t>ソルベブルー</t>
         </is>
       </c>
-      <c r="F79" s="3" t="inlineStr">
+      <c r="F87" s="3" t="inlineStr">
         <is>
           <t>サクラ_正面_パネルなし_カラー1_ソルベブルー</t>
         </is>
       </c>
-      <c r="G79" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" s="6" t="inlineStr">
+      <c r="G87" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="6" t="inlineStr">
         <is>
           <t>サクラ</t>
         </is>
       </c>
-      <c r="B80" s="6" t="inlineStr">
+      <c r="B88" s="6" t="inlineStr">
         <is>
           <t>正面</t>
         </is>
       </c>
-      <c r="C80" s="6" t="inlineStr">
+      <c r="C88" s="6" t="inlineStr">
         <is>
           <t>パネルなし</t>
         </is>
       </c>
-      <c r="D80" s="6" t="inlineStr">
+      <c r="D88" s="6" t="inlineStr">
         <is>
           <t>カラー2</t>
         </is>
       </c>
-      <c r="E80" s="6" t="inlineStr">
+      <c r="E88" s="6" t="inlineStr">
         <is>
           <t>スパークリングレッド</t>
         </is>
       </c>
-      <c r="F80" s="3" t="inlineStr">
+      <c r="F88" s="3" t="inlineStr">
         <is>
           <t>サクラ_正面_パネルなし_カラー2_スパークリングレッド</t>
         </is>
       </c>
-      <c r="G80" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" s="6" t="inlineStr">
+      <c r="G88" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="6" t="inlineStr">
         <is>
           <t>サクラ</t>
         </is>
       </c>
-      <c r="B81" s="6" t="inlineStr">
+      <c r="B89" s="6" t="inlineStr">
         <is>
           <t>正面</t>
         </is>
       </c>
-      <c r="C81" s="6" t="inlineStr">
+      <c r="C89" s="6" t="inlineStr">
         <is>
           <t>ボンネット＋ルーフ</t>
         </is>
       </c>
-      <c r="D81" s="6" t="inlineStr">
+      <c r="D89" s="6" t="inlineStr">
         <is>
           <t>白</t>
         </is>
       </c>
-      <c r="E81" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F81" s="3" t="inlineStr">
+      <c r="E89" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F89" s="3" t="inlineStr">
         <is>
           <t>サクラ_正面_ボンネット＋ルーフ_白</t>
         </is>
       </c>
-      <c r="G81" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" s="6" t="inlineStr">
+      <c r="G89" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="6" t="inlineStr">
         <is>
           <t>サクラ</t>
         </is>
       </c>
-      <c r="B82" s="6" t="inlineStr">
+      <c r="B90" s="6" t="inlineStr">
         <is>
           <t>正面</t>
         </is>
       </c>
-      <c r="C82" s="6" t="inlineStr">
+      <c r="C90" s="6" t="inlineStr">
         <is>
           <t>ボンネット＋ルーフ</t>
         </is>
       </c>
-      <c r="D82" s="6" t="inlineStr">
+      <c r="D90" s="6" t="inlineStr">
         <is>
           <t>黒</t>
         </is>
       </c>
-      <c r="E82" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F82" s="3" t="inlineStr">
+      <c r="E90" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F90" s="3" t="inlineStr">
         <is>
           <t>サクラ_正面_ボンネット＋ルーフ_黒</t>
         </is>
       </c>
-      <c r="G82" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" s="6" t="inlineStr">
+      <c r="G90" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="6" t="inlineStr">
         <is>
           <t>サクラ</t>
         </is>
       </c>
-      <c r="B83" s="6" t="inlineStr">
+      <c r="B91" s="6" t="inlineStr">
         <is>
           <t>正面</t>
         </is>
       </c>
-      <c r="C83" s="6" t="inlineStr">
+      <c r="C91" s="6" t="inlineStr">
         <is>
           <t>ボンネット＋ルーフ</t>
         </is>
       </c>
-      <c r="D83" s="6" t="inlineStr">
+      <c r="D91" s="6" t="inlineStr">
         <is>
           <t>カラー1</t>
         </is>
       </c>
-      <c r="E83" s="6" t="inlineStr">
+      <c r="E91" s="6" t="inlineStr">
         <is>
           <t>ソルベブルー</t>
         </is>
       </c>
-      <c r="F83" s="3" t="inlineStr">
+      <c r="F91" s="3" t="inlineStr">
         <is>
           <t>サクラ_正面_ボンネット＋ルーフ_カラー1_ソルベブルー</t>
         </is>
       </c>
-      <c r="G83" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" s="6" t="inlineStr">
+      <c r="G91" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="6" t="inlineStr">
         <is>
           <t>サクラ</t>
         </is>
       </c>
-      <c r="B84" s="6" t="inlineStr">
+      <c r="B92" s="6" t="inlineStr">
         <is>
           <t>正面</t>
         </is>
       </c>
-      <c r="C84" s="6" t="inlineStr">
+      <c r="C92" s="6" t="inlineStr">
         <is>
           <t>ボンネット＋ルーフ</t>
         </is>
       </c>
-      <c r="D84" s="6" t="inlineStr">
+      <c r="D92" s="6" t="inlineStr">
         <is>
           <t>カラー2</t>
         </is>
       </c>
-      <c r="E84" s="6" t="inlineStr">
+      <c r="E92" s="6" t="inlineStr">
         <is>
           <t>スパークリングレッド</t>
         </is>
       </c>
-      <c r="F84" s="3" t="inlineStr">
+      <c r="F92" s="3" t="inlineStr">
         <is>
           <t>サクラ_正面_ボンネット＋ルーフ_カラー2_スパークリングレッド</t>
         </is>
       </c>
-      <c r="G84" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" s="8" t="inlineStr">
+      <c r="G92" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="8" t="inlineStr">
         <is>
           <t>サクラ</t>
         </is>
       </c>
-      <c r="B85" s="8" t="inlineStr">
+      <c r="B93" s="8" t="inlineStr">
         <is>
           <t>真後ろ</t>
         </is>
       </c>
-      <c r="C85" s="8" t="inlineStr">
+      <c r="C93" s="8" t="inlineStr">
         <is>
           <t>パネル有りなし併用</t>
         </is>
       </c>
-      <c r="D85" s="8" t="inlineStr">
+      <c r="D93" s="8" t="inlineStr">
         <is>
           <t>白</t>
         </is>
       </c>
-      <c r="E85" s="8" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F85" s="3" t="inlineStr">
+      <c r="E93" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F93" s="3" t="inlineStr">
         <is>
           <t>サクラ_真後ろ_パネル有りなし併用_白</t>
         </is>
       </c>
-      <c r="G85" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" s="8" t="inlineStr">
+      <c r="G93" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="8" t="inlineStr">
         <is>
           <t>サクラ</t>
         </is>
       </c>
-      <c r="B86" s="8" t="inlineStr">
+      <c r="B94" s="8" t="inlineStr">
         <is>
           <t>真後ろ</t>
         </is>
       </c>
-      <c r="C86" s="8" t="inlineStr">
+      <c r="C94" s="8" t="inlineStr">
         <is>
           <t>パネル有りなし併用</t>
         </is>
       </c>
-      <c r="D86" s="8" t="inlineStr">
+      <c r="D94" s="8" t="inlineStr">
         <is>
           <t>黒</t>
         </is>
       </c>
-      <c r="E86" s="8" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F86" s="3" t="inlineStr">
+      <c r="E94" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F94" s="3" t="inlineStr">
         <is>
           <t>サクラ_真後ろ_パネル有りなし併用_黒</t>
         </is>
       </c>
-      <c r="G86" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" s="8" t="inlineStr">
+      <c r="G94" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="8" t="inlineStr">
         <is>
           <t>サクラ</t>
         </is>
       </c>
-      <c r="B87" s="8" t="inlineStr">
+      <c r="B95" s="8" t="inlineStr">
         <is>
           <t>真後ろ</t>
         </is>
       </c>
-      <c r="C87" s="8" t="inlineStr">
+      <c r="C95" s="8" t="inlineStr">
         <is>
           <t>パネル有りなし併用</t>
         </is>
       </c>
-      <c r="D87" s="8" t="inlineStr">
+      <c r="D95" s="8" t="inlineStr">
         <is>
           <t>カラー1</t>
         </is>
       </c>
-      <c r="E87" s="8" t="inlineStr">
+      <c r="E95" s="8" t="inlineStr">
         <is>
           <t>ソルベブルー</t>
         </is>
       </c>
-      <c r="F87" s="3" t="inlineStr">
+      <c r="F95" s="3" t="inlineStr">
         <is>
           <t>サクラ_真後ろ_パネル有りなし併用_カラー1_ソルベブルー</t>
         </is>
       </c>
-      <c r="G87" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" s="8" t="inlineStr">
+      <c r="G95" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="8" t="inlineStr">
         <is>
           <t>サクラ</t>
         </is>
       </c>
-      <c r="B88" s="8" t="inlineStr">
+      <c r="B96" s="8" t="inlineStr">
         <is>
           <t>真後ろ</t>
         </is>
       </c>
-      <c r="C88" s="8" t="inlineStr">
+      <c r="C96" s="8" t="inlineStr">
         <is>
           <t>パネル有りなし併用</t>
         </is>
       </c>
-      <c r="D88" s="8" t="inlineStr">
+      <c r="D96" s="8" t="inlineStr">
         <is>
           <t>カラー2</t>
         </is>
       </c>
-      <c r="E88" s="8" t="inlineStr">
+      <c r="E96" s="8" t="inlineStr">
         <is>
           <t>スパークリングレッド</t>
         </is>
       </c>
-      <c r="F88" s="3" t="inlineStr">
+      <c r="F96" s="3" t="inlineStr">
         <is>
           <t>サクラ_真後ろ_パネル有りなし併用_カラー2_スパークリングレッド</t>
         </is>
       </c>
-      <c r="G88" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
+      <c r="G96" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="9" t="inlineStr">
+        <is>
+          <t>サクラ</t>
+        </is>
+      </c>
+      <c r="B97" s="9" t="inlineStr">
+        <is>
+          <t>パーツカラー（斜め上）</t>
+        </is>
+      </c>
+      <c r="C97" s="9" t="inlineStr">
+        <is>
+          <t>ルーフ＋ボンネット</t>
+        </is>
+      </c>
+      <c r="D97" s="9" t="inlineStr">
+        <is>
+          <t>白</t>
+        </is>
+      </c>
+      <c r="E97" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F97" s="10" t="inlineStr">
+        <is>
+          <t>サクラ_斜め上_ルーフ＋ボンネット_白_パーツカラー</t>
+        </is>
+      </c>
+      <c r="G97" s="7" t="inlineStr">
+        <is>
+          <t>✗ 要作成</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="9" t="inlineStr">
+        <is>
+          <t>サクラ</t>
+        </is>
+      </c>
+      <c r="B98" s="9" t="inlineStr">
+        <is>
+          <t>パーツカラー（斜め上）</t>
+        </is>
+      </c>
+      <c r="C98" s="9" t="inlineStr">
+        <is>
+          <t>ルーフ＋ボンネット</t>
+        </is>
+      </c>
+      <c r="D98" s="9" t="inlineStr">
+        <is>
+          <t>黒</t>
+        </is>
+      </c>
+      <c r="E98" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F98" s="10" t="inlineStr">
+        <is>
+          <t>サクラ_斜め上_ルーフ＋ボンネット_黒_パーツカラー</t>
+        </is>
+      </c>
+      <c r="G98" s="7" t="inlineStr">
+        <is>
+          <t>✗ 要作成</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="11" t="inlineStr">
+        <is>
+          <t>サクラ</t>
+        </is>
+      </c>
+      <c r="B99" s="11" t="inlineStr">
+        <is>
+          <t>パーツカラー（リアガラス）</t>
+        </is>
+      </c>
+      <c r="C99" s="11" t="inlineStr">
+        <is>
+          <t>リアガラス＋ルーフ</t>
+        </is>
+      </c>
+      <c r="D99" s="11" t="inlineStr">
+        <is>
+          <t>白</t>
+        </is>
+      </c>
+      <c r="E99" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F99" s="10" t="inlineStr">
+        <is>
+          <t>サクラ_リアガラス_パーツカラー_白</t>
+        </is>
+      </c>
+      <c r="G99" s="7" t="inlineStr">
+        <is>
+          <t>✗ 要作成</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="11" t="inlineStr">
+        <is>
+          <t>サクラ</t>
+        </is>
+      </c>
+      <c r="B100" s="11" t="inlineStr">
+        <is>
+          <t>パーツカラー（リアガラス）</t>
+        </is>
+      </c>
+      <c r="C100" s="11" t="inlineStr">
+        <is>
+          <t>リアガラス＋ルーフ</t>
+        </is>
+      </c>
+      <c r="D100" s="11" t="inlineStr">
+        <is>
+          <t>黒</t>
+        </is>
+      </c>
+      <c r="E100" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F100" s="10" t="inlineStr">
+        <is>
+          <t>サクラ_リアガラス_パーツカラー_黒</t>
+        </is>
+      </c>
+      <c r="G100" s="7" t="inlineStr">
+        <is>
+          <t>✗ 要作成</t>
         </is>
       </c>
     </row>
